--- a/templates/tonnage_template.xlsx
+++ b/templates/tonnage_template.xlsx
@@ -400,7 +400,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>必须填写中国、示例国籍、中国澳门三个值的其中一个</t>
+          <t>必须填写中国、中国香港、中国澳门三个值的其中一个</t>
         </r>
         <r>
           <rPr>
@@ -1883,7 +1883,7 @@
     </r>
   </si>
   <si>
-    <t>IMO:1234567</t>
+    <t>IMO:1116648</t>
   </si>
   <si>
     <r>
@@ -2005,10 +2005,10 @@
     </r>
   </si>
   <si>
-    <t>示例船务代理有限公司</t>
-  </si>
-  <si>
-    <t>联系人</t>
+    <t>广州港中联国际船务代理有限公司</t>
+  </si>
+  <si>
+    <t>白树辉</t>
   </si>
   <si>
     <t>香港</t>
@@ -3237,7 +3237,7 @@
     </r>
   </si>
   <si>
-    <t>示例国籍</t>
+    <t>中国香港</t>
   </si>
   <si>
     <t>HONGKONG</t>
@@ -3487,7 +3487,7 @@
     <t>Montenegro</t>
   </si>
   <si>
-    <t>TEST0001</t>
+    <t>B42BR8005</t>
   </si>
   <si>
     <t>名单版本是正确的</t>
@@ -3505,7 +3505,7 @@
     <t>S</t>
   </si>
   <si>
-    <t>TEST0002</t>
+    <t>AB498691</t>
   </si>
   <si>
     <t>Second Officer</t>
@@ -3514,148 +3514,148 @@
     <t>Filipino</t>
   </si>
   <si>
-    <t>TEST0003</t>
-  </si>
-  <si>
-    <t>赵六</t>
+    <t>P0392496A</t>
+  </si>
+  <si>
+    <t>GONZAGA JOHN BRIAN CANALITA</t>
   </si>
   <si>
     <t>Third Officer</t>
   </si>
   <si>
-    <t>TEST0004</t>
-  </si>
-  <si>
-    <t>钱七</t>
+    <t>EC3697674</t>
+  </si>
+  <si>
+    <t>DYACHENKO VASYL</t>
   </si>
   <si>
     <t>Chief Engineer</t>
   </si>
   <si>
-    <t>TEST0005</t>
-  </si>
-  <si>
-    <t>孙八</t>
+    <t>AB406216</t>
+  </si>
+  <si>
+    <t>BALAKIN OLEG</t>
   </si>
   <si>
     <t>Second Engineer</t>
   </si>
   <si>
-    <t>TEST0006</t>
-  </si>
-  <si>
-    <t>周九</t>
+    <t>AB565162</t>
+  </si>
+  <si>
+    <t>BACERDO OMAR DAMES</t>
   </si>
   <si>
     <t>Junior Engineer</t>
   </si>
   <si>
-    <t>TEST0007</t>
-  </si>
-  <si>
-    <t>吴十</t>
+    <t>P1649209A</t>
+  </si>
+  <si>
+    <t>SANTACERA ROTSEN MAR DAYADAY</t>
   </si>
   <si>
     <t xml:space="preserve"> Junior Electrician</t>
   </si>
   <si>
-    <t>TEST0008</t>
-  </si>
-  <si>
-    <t>郑一</t>
+    <t>P1399821A</t>
+  </si>
+  <si>
+    <t>JAVIER EDGAR AMMEN</t>
   </si>
   <si>
     <t>Bosun</t>
   </si>
   <si>
-    <t>TEST0009</t>
-  </si>
-  <si>
-    <t>王一</t>
+    <t>EC4641553</t>
+  </si>
+  <si>
+    <t>ELPA KENNETH BLANCO</t>
   </si>
   <si>
     <t>Able Seaman</t>
   </si>
   <si>
-    <t>TEST0010</t>
-  </si>
-  <si>
-    <t>李一</t>
-  </si>
-  <si>
-    <t>TEST0011</t>
-  </si>
-  <si>
-    <t>赵一</t>
-  </si>
-  <si>
-    <t>TEST0012</t>
-  </si>
-  <si>
-    <t>陈一</t>
+    <t>P2512380A</t>
+  </si>
+  <si>
+    <t>FLORENTINO JOEMARIE LACHICA</t>
+  </si>
+  <si>
+    <t>EC6525043</t>
+  </si>
+  <si>
+    <t>SUAREZ JETTE ANTHONY CAPANAS</t>
+  </si>
+  <si>
+    <t>P0863919A</t>
+  </si>
+  <si>
+    <t>JAMERO IANJAY HAMOAY</t>
   </si>
   <si>
     <t>Ordinary Seaman</t>
   </si>
   <si>
-    <t>TEST0013</t>
-  </si>
-  <si>
-    <t>刘一</t>
-  </si>
-  <si>
-    <t>TEST0014</t>
-  </si>
-  <si>
-    <t>杨一</t>
+    <t>EC5956980</t>
+  </si>
+  <si>
+    <t>PELLETERO ALLEN SEGISMUNDO</t>
+  </si>
+  <si>
+    <t>P3925249A</t>
+  </si>
+  <si>
+    <t>OLOJAN ROSEN JUANICO</t>
   </si>
   <si>
     <t>Fitter</t>
   </si>
   <si>
-    <t>TEST0015</t>
-  </si>
-  <si>
-    <t>黄一</t>
+    <t>EC4389049</t>
+  </si>
+  <si>
+    <t>CAMILOTE GEOFFREY CALETINA</t>
   </si>
   <si>
     <t>Oiler</t>
   </si>
   <si>
-    <t>TEST0016</t>
-  </si>
-  <si>
-    <t>周一</t>
+    <t>P2263420A</t>
+  </si>
+  <si>
+    <t>ECAT JOSEPH PAUL TENEBRO</t>
   </si>
   <si>
     <t>Wiper</t>
   </si>
   <si>
-    <t>TEST0017</t>
-  </si>
-  <si>
-    <t>吴一</t>
-  </si>
-  <si>
-    <t>TEST0018</t>
-  </si>
-  <si>
-    <t>徐一</t>
+    <t>P3596511A</t>
+  </si>
+  <si>
+    <t>DELIS  EUGENE SALIGUMBA</t>
+  </si>
+  <si>
+    <t>EC5270716</t>
+  </si>
+  <si>
+    <t>MOGRO ROMELITO LOSTE</t>
   </si>
   <si>
     <t>Chief Cook</t>
   </si>
   <si>
-    <t>TEST0019</t>
-  </si>
-  <si>
-    <t>孙一</t>
+    <t>EC2844651</t>
+  </si>
+  <si>
+    <t>CAMANAY JONATHAN SUAZO</t>
   </si>
   <si>
     <t>Messboy</t>
   </si>
   <si>
-    <t>TEST0020</t>
+    <t>EC8290337</t>
   </si>
   <si>
     <t>12. Date and signature by master, authorized by agent or officer</t>
@@ -4074,7 +4074,7 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>/TEST0001</t>
+      <t>/P4794223A</t>
     </r>
   </si>
   <si>
@@ -4149,7 +4149,7 @@
     <t>Signature of Master:</t>
   </si>
   <si>
-    <t>Example Shipping Agency Co., Ltd.</t>
+    <t>Guangzhou Port Unitrans Agency Co., Ltd.</t>
   </si>
   <si>
     <r>
@@ -4190,25 +4190,25 @@
     <t>于洪涛</t>
   </si>
   <si>
-    <t>李四</t>
-  </si>
-  <si>
-    <t>TEST0008</t>
-  </si>
-  <si>
-    <t>王五</t>
+    <t>BILINS'KY ANDRIY</t>
+  </si>
+  <si>
+    <t>ET549562</t>
+  </si>
+  <si>
+    <t>OGANA ROGELIO PENTON</t>
   </si>
   <si>
     <t>DIACHENKO VASYL</t>
   </si>
   <si>
-    <t>TEST0009</t>
-  </si>
-  <si>
-    <t>TEST0010</t>
-  </si>
-  <si>
-    <t>王五</t>
+    <t>ET112764</t>
+  </si>
+  <si>
+    <t>ET529509</t>
+  </si>
+  <si>
+    <t>BILANGO JEAN CONSULAR</t>
   </si>
   <si>
     <t>F</t>
@@ -4223,10 +4223,10 @@
     <t>SAN MIGUEL BULACAN</t>
   </si>
   <si>
-    <t>TEST0011</t>
-  </si>
-  <si>
-    <t>交通运营单位：示例船务代理有限公司</t>
+    <t>EB9781010</t>
+  </si>
+  <si>
+    <t>交通运营单位：广州联合国际船舶代理有限公司</t>
   </si>
   <si>
     <t xml:space="preserve">移交时间：                        </t>
@@ -4567,7 +4567,7 @@
     <t>Container</t>
   </si>
   <si>
-    <t>IMO:1234567</t>
+    <t>IMO:9987574</t>
   </si>
   <si>
     <t>10086/782</t>
@@ -5074,7 +5074,7 @@
     <t>所有人</t>
   </si>
   <si>
-    <t>示例船公司中国航运</t>
+    <t>马士基中国航运</t>
   </si>
   <si>
     <t>Registration/IMO No.</t>
@@ -5448,7 +5448,7 @@
     <t>本表加附在报检面单之后</t>
   </si>
   <si>
-    <t>示例船务代理有限公司</t>
+    <t>广州联合国际船舶代理有限公司</t>
   </si>
   <si>
     <t>IN</t>
@@ -5469,7 +5469,7 @@
     <t>MANILA</t>
   </si>
   <si>
-    <t>金额：1000</t>
+    <t>金额：112092.8</t>
   </si>
   <si>
     <t>船舶吨税执照申请书</t>
@@ -5877,11 +5877,11 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>13800000000</t>
+      <t>39080209</t>
     </r>
   </si>
   <si>
-    <t>传真：（8620）13800000000</t>
+    <t>传真：（8620）39080620</t>
   </si>
   <si>
     <r>
@@ -5901,7 +5901,7 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>example@example.com</t>
+      <t>uniscogzns@vip.163.com</t>
     </r>
   </si>
   <si>
@@ -20244,7 +20244,7 @@
       </c>
       <c r="F8" s="1208" t="str">
         <f>'Gen Inb'!I10</f>
-        <v>IMO:1234567</v>
+        <v>IMO:1116648</v>
       </c>
       <c r="G8" s="1208"/>
       <c r="H8" s="1205"/>
@@ -21058,7 +21058,7 @@
     <row r="2" spans="1:11">
       <c r="A2" s="1217" t="str">
         <f>IF('Crew Inb'!K11="","",'Crew Inb'!K11)</f>
-        <v>TEST0001</v>
+        <v>B42BR8005</v>
       </c>
       <c r="B2" t="str">
         <f>IF('Crew Inb'!J11="","",IF('Crew Inb'!J11="P","普通护照",IF('Crew Inb'!J11="S","海员证","")))</f>
@@ -21090,7 +21090,7 @@
     <row r="3" spans="1:11">
       <c r="A3" t="str">
         <f>IF('Crew Inb'!K12="","",'Crew Inb'!K12)</f>
-        <v>TEST0002</v>
+        <v>AB498691</v>
       </c>
       <c r="B3" t="str">
         <f>IF('Crew Inb'!J12="","",IF('Crew Inb'!J12="P","普通护照",IF('Crew Inb'!J12="S","海员证","")))</f>
@@ -21122,7 +21122,7 @@
     <row r="4" spans="1:11">
       <c r="A4" t="str">
         <f>IF('Crew Inb'!K13="","",'Crew Inb'!K13)</f>
-        <v>TEST0003</v>
+        <v>P0392496A</v>
       </c>
       <c r="B4" t="str">
         <f>IF('Crew Inb'!J13="","",IF('Crew Inb'!J13="P","普通护照",IF('Crew Inb'!J13="S","海员证","")))</f>
@@ -21154,7 +21154,7 @@
     <row r="5" spans="1:11">
       <c r="A5" t="str">
         <f>IF('Crew Inb'!K14="","",'Crew Inb'!K14)</f>
-        <v>TEST0004</v>
+        <v>EC3697674</v>
       </c>
       <c r="B5" t="str">
         <f>IF('Crew Inb'!J14="","",IF('Crew Inb'!J14="P","普通护照",IF('Crew Inb'!J14="S","海员证","")))</f>
@@ -21165,7 +21165,7 @@
       </c>
       <c r="D5" t="str">
         <f>IF('Crew Inb'!C14="","",'Crew Inb'!C14&amp;" "&amp;'Crew Inb'!D14)</f>
-        <v>赵六 </v>
+        <v>GONZAGA JOHN BRIAN CANALITA </v>
       </c>
       <c r="E5" t="str">
         <f>IF('Crew Inb'!E14="","",IF('Crew Inb'!E14="M","男",IF('Crew Inb'!E14="F","女","未说明")))</f>
@@ -21186,7 +21186,7 @@
     <row r="6" spans="1:11">
       <c r="A6" t="str">
         <f>IF('Crew Inb'!K15="","",'Crew Inb'!K15)</f>
-        <v>TEST0005</v>
+        <v>AB406216</v>
       </c>
       <c r="B6" t="str">
         <f>IF('Crew Inb'!J15="","",IF('Crew Inb'!J15="P","普通护照",IF('Crew Inb'!J15="S","海员证","")))</f>
@@ -21197,7 +21197,7 @@
       </c>
       <c r="D6" t="str">
         <f>IF('Crew Inb'!C15="","",'Crew Inb'!C15&amp;" "&amp;'Crew Inb'!D15)</f>
-        <v>钱七 </v>
+        <v>DYACHENKO VASYL </v>
       </c>
       <c r="E6" t="str">
         <f>IF('Crew Inb'!E15="","",IF('Crew Inb'!E15="M","男",IF('Crew Inb'!E15="F","女","未说明")))</f>
@@ -21218,7 +21218,7 @@
     <row r="7" spans="1:11">
       <c r="A7" t="str">
         <f>IF('Crew Inb'!K16="","",'Crew Inb'!K16)</f>
-        <v>TEST0006</v>
+        <v>AB565162</v>
       </c>
       <c r="B7" t="str">
         <f>IF('Crew Inb'!J16="","",IF('Crew Inb'!J16="P","普通护照",IF('Crew Inb'!J16="S","海员证","")))</f>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="D7" t="str">
         <f>IF('Crew Inb'!C16="","",'Crew Inb'!C16&amp;" "&amp;'Crew Inb'!D16)</f>
-        <v>孙八 </v>
+        <v>BALAKIN OLEG </v>
       </c>
       <c r="E7" t="str">
         <f>IF('Crew Inb'!E16="","",IF('Crew Inb'!E16="M","男",IF('Crew Inb'!E16="F","女","未说明")))</f>
@@ -21250,7 +21250,7 @@
     <row r="8" spans="1:11">
       <c r="A8" t="str">
         <f>IF('Crew Inb'!K17="","",'Crew Inb'!K17)</f>
-        <v>TEST0007</v>
+        <v>P1649209A</v>
       </c>
       <c r="B8" t="str">
         <f>IF('Crew Inb'!J17="","",IF('Crew Inb'!J17="P","普通护照",IF('Crew Inb'!J17="S","海员证","")))</f>
@@ -21261,7 +21261,7 @@
       </c>
       <c r="D8" t="str">
         <f>IF('Crew Inb'!C17="","",'Crew Inb'!C17&amp;" "&amp;'Crew Inb'!D17)</f>
-        <v>周九 </v>
+        <v>BACERDO OMAR DAMES </v>
       </c>
       <c r="E8" t="str">
         <f>IF('Crew Inb'!E17="","",IF('Crew Inb'!E17="M","男",IF('Crew Inb'!E17="F","女","未说明")))</f>
@@ -21282,7 +21282,7 @@
     <row r="9" spans="1:11">
       <c r="A9" t="str">
         <f>IF('Crew Inb'!K18="","",'Crew Inb'!K18)</f>
-        <v>TEST0008</v>
+        <v>P1399821A</v>
       </c>
       <c r="B9" t="str">
         <f>IF('Crew Inb'!J18="","",IF('Crew Inb'!J18="P","普通护照",IF('Crew Inb'!J18="S","海员证","")))</f>
@@ -21293,7 +21293,7 @@
       </c>
       <c r="D9" t="str">
         <f>IF('Crew Inb'!C18="","",'Crew Inb'!C18&amp;" "&amp;'Crew Inb'!D18)</f>
-        <v>吴十 </v>
+        <v>SANTACERA ROTSEN MAR DAYADAY </v>
       </c>
       <c r="E9" t="str">
         <f>IF('Crew Inb'!E18="","",IF('Crew Inb'!E18="M","男",IF('Crew Inb'!E18="F","女","未说明")))</f>
@@ -21346,7 +21346,7 @@
     <row r="11" spans="1:11">
       <c r="A11" t="str">
         <f>IF('Crew Inb'!K19="","",'Crew Inb'!K19)</f>
-        <v>TEST0009</v>
+        <v>EC4641553</v>
       </c>
       <c r="B11" t="str">
         <f>IF('Crew Inb'!J19="","",IF('Crew Inb'!J19="P","普通护照",IF('Crew Inb'!J19="S","海员证","")))</f>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="D11" t="str">
         <f>IF('Crew Inb'!C19="","",'Crew Inb'!C19&amp;" "&amp;'Crew Inb'!D19)</f>
-        <v>郑一 </v>
+        <v>JAVIER EDGAR AMMEN </v>
       </c>
       <c r="E11" t="str">
         <f>IF('Crew Inb'!E19="","",IF('Crew Inb'!E19="M","男",IF('Crew Inb'!E19="F","女","未说明")))</f>
@@ -21378,7 +21378,7 @@
     <row r="12" spans="1:11">
       <c r="A12" t="str">
         <f>IF('Crew Inb'!K20="","",'Crew Inb'!K20)</f>
-        <v>TEST0010</v>
+        <v>P2512380A</v>
       </c>
       <c r="B12" t="str">
         <f>IF('Crew Inb'!J20="","",IF('Crew Inb'!J20="P","普通护照",IF('Crew Inb'!J20="S","海员证","")))</f>
@@ -21389,7 +21389,7 @@
       </c>
       <c r="D12" t="str">
         <f>IF('Crew Inb'!C20="","",'Crew Inb'!C20&amp;" "&amp;'Crew Inb'!D20)</f>
-        <v>王一 </v>
+        <v>ELPA KENNETH BLANCO </v>
       </c>
       <c r="E12" t="str">
         <f>IF('Crew Inb'!E20="","",IF('Crew Inb'!E20="M","男",IF('Crew Inb'!E20="F","女","未说明")))</f>
@@ -21410,7 +21410,7 @@
     <row r="13" spans="1:11">
       <c r="A13" t="str">
         <f>IF('Crew Inb'!K21="","",'Crew Inb'!K21)</f>
-        <v>TEST0011</v>
+        <v>EC6525043</v>
       </c>
       <c r="B13" t="str">
         <f>IF('Crew Inb'!J21="","",IF('Crew Inb'!J21="P","普通护照",IF('Crew Inb'!J21="S","海员证","")))</f>
@@ -21421,7 +21421,7 @@
       </c>
       <c r="D13" t="str">
         <f>IF('Crew Inb'!C21="","",'Crew Inb'!C21&amp;" "&amp;'Crew Inb'!D21)</f>
-        <v>李一 </v>
+        <v>FLORENTINO JOEMARIE LACHICA </v>
       </c>
       <c r="E13" t="str">
         <f>IF('Crew Inb'!E21="","",IF('Crew Inb'!E21="M","男",IF('Crew Inb'!E21="F","女","未说明")))</f>
@@ -21442,7 +21442,7 @@
     <row r="14" spans="1:11">
       <c r="A14" t="str">
         <f>IF('Crew Inb'!K22="","",'Crew Inb'!K22)</f>
-        <v>TEST0012</v>
+        <v>P0863919A</v>
       </c>
       <c r="B14" t="str">
         <f>IF('Crew Inb'!J22="","",IF('Crew Inb'!J22="P","普通护照",IF('Crew Inb'!J22="S","海员证","")))</f>
@@ -21453,7 +21453,7 @@
       </c>
       <c r="D14" t="str">
         <f>IF('Crew Inb'!C22="","",'Crew Inb'!C22&amp;" "&amp;'Crew Inb'!D22)</f>
-        <v>赵一 </v>
+        <v>SUAREZ JETTE ANTHONY CAPANAS </v>
       </c>
       <c r="E14" t="str">
         <f>IF('Crew Inb'!E22="","",IF('Crew Inb'!E22="M","男",IF('Crew Inb'!E22="F","女","未说明")))</f>
@@ -21474,7 +21474,7 @@
     <row r="15" spans="1:11">
       <c r="A15" t="str">
         <f>IF('Crew Inb'!K23="","",'Crew Inb'!K23)</f>
-        <v>TEST0013</v>
+        <v>EC5956980</v>
       </c>
       <c r="B15" t="str">
         <f>IF('Crew Inb'!J23="","",IF('Crew Inb'!J23="P","普通护照",IF('Crew Inb'!J23="S","海员证","")))</f>
@@ -21485,7 +21485,7 @@
       </c>
       <c r="D15" t="str">
         <f>IF('Crew Inb'!C23="","",'Crew Inb'!C23&amp;" "&amp;'Crew Inb'!D23)</f>
-        <v>陈一 </v>
+        <v>JAMERO IANJAY HAMOAY </v>
       </c>
       <c r="E15" t="str">
         <f>IF('Crew Inb'!E23="","",IF('Crew Inb'!E23="M","男",IF('Crew Inb'!E23="F","女","未说明")))</f>
@@ -21506,7 +21506,7 @@
     <row r="16" spans="1:11">
       <c r="A16" t="str">
         <f>IF('Crew Inb'!K24="","",'Crew Inb'!K24)</f>
-        <v>TEST0014</v>
+        <v>P3925249A</v>
       </c>
       <c r="B16" t="str">
         <f>IF('Crew Inb'!J24="","",IF('Crew Inb'!J24="P","普通护照",IF('Crew Inb'!J24="S","海员证","")))</f>
@@ -21517,7 +21517,7 @@
       </c>
       <c r="D16" t="str">
         <f>IF('Crew Inb'!C24="","",'Crew Inb'!C24&amp;" "&amp;'Crew Inb'!D24)</f>
-        <v>刘一 </v>
+        <v>PELLETERO ALLEN SEGISMUNDO </v>
       </c>
       <c r="E16" t="str">
         <f>IF('Crew Inb'!E24="","",IF('Crew Inb'!E24="M","男",IF('Crew Inb'!E24="F","女","未说明")))</f>
@@ -21538,7 +21538,7 @@
     <row r="17" spans="1:8">
       <c r="A17" t="str">
         <f>IF('Crew Inb'!K25="","",'Crew Inb'!K25)</f>
-        <v>TEST0015</v>
+        <v>EC4389049</v>
       </c>
       <c r="B17" t="str">
         <f>IF('Crew Inb'!J25="","",IF('Crew Inb'!J25="P","普通护照",IF('Crew Inb'!J25="S","海员证","")))</f>
@@ -21549,7 +21549,7 @@
       </c>
       <c r="D17" t="str">
         <f>IF('Crew Inb'!C25="","",'Crew Inb'!C25&amp;" "&amp;'Crew Inb'!D25)</f>
-        <v>杨一 </v>
+        <v>OLOJAN ROSEN JUANICO </v>
       </c>
       <c r="E17" t="str">
         <f>IF('Crew Inb'!E25="","",IF('Crew Inb'!E25="M","男",IF('Crew Inb'!E25="F","女","未说明")))</f>
@@ -21570,7 +21570,7 @@
     <row r="18" spans="1:8">
       <c r="A18" t="str">
         <f>IF('Crew Inb'!K26="","",'Crew Inb'!K26)</f>
-        <v>TEST0016</v>
+        <v>P2263420A</v>
       </c>
       <c r="B18" t="str">
         <f>IF('Crew Inb'!J26="","",IF('Crew Inb'!J26="P","普通护照",IF('Crew Inb'!J26="S","海员证","")))</f>
@@ -21581,7 +21581,7 @@
       </c>
       <c r="D18" t="str">
         <f>IF('Crew Inb'!C26="","",'Crew Inb'!C26&amp;" "&amp;'Crew Inb'!D26)</f>
-        <v>黄一 </v>
+        <v>CAMILOTE GEOFFREY CALETINA </v>
       </c>
       <c r="E18" t="str">
         <f>IF('Crew Inb'!E26="","",IF('Crew Inb'!E26="M","男",IF('Crew Inb'!E26="F","女","未说明")))</f>
@@ -21602,7 +21602,7 @@
     <row r="19" spans="1:8">
       <c r="A19" t="str">
         <f>IF('Crew Inb'!K27="","",'Crew Inb'!K27)</f>
-        <v>TEST0017</v>
+        <v>P3596511A</v>
       </c>
       <c r="B19" t="str">
         <f>IF('Crew Inb'!J27="","",IF('Crew Inb'!J27="P","普通护照",IF('Crew Inb'!J27="S","海员证","")))</f>
@@ -21613,7 +21613,7 @@
       </c>
       <c r="D19" t="str">
         <f>IF('Crew Inb'!C27="","",'Crew Inb'!C27&amp;" "&amp;'Crew Inb'!D27)</f>
-        <v>周一 </v>
+        <v>ECAT JOSEPH PAUL TENEBRO </v>
       </c>
       <c r="E19" t="str">
         <f>IF('Crew Inb'!E27="","",IF('Crew Inb'!E27="M","男",IF('Crew Inb'!E27="F","女","未说明")))</f>
@@ -22845,7 +22845,7 @@
       <c r="C6" s="569"/>
       <c r="D6" s="570" t="str">
         <f>'Gen Inb'!I10</f>
-        <v>IMO:1234567</v>
+        <v>IMO:1116648</v>
       </c>
       <c r="E6" s="570"/>
       <c r="F6" s="571"/>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="R9" s="418" t="str">
         <f>'Gen Inb'!I10</f>
-        <v>IMO:1234567</v>
+        <v>IMO:1116648</v>
       </c>
       <c r="S9" s="418"/>
       <c r="T9" s="418"/>
@@ -29245,7 +29245,7 @@
       <c r="F21" s="393"/>
       <c r="G21" s="401"/>
       <c r="H21" s="393">
-        <v>1234567</v>
+        <v>1050189</v>
       </c>
       <c r="I21" s="393"/>
       <c r="J21" s="396">
@@ -29256,7 +29256,7 @@
     <row r="22" ht="24" customHeight="1" spans="2:13">
       <c r="B22" s="401"/>
       <c r="C22" s="393">
-        <v>1234567</v>
+        <v>1047976</v>
       </c>
       <c r="D22" s="393"/>
       <c r="E22" s="396">
@@ -29265,7 +29265,7 @@
       <c r="F22" s="393"/>
       <c r="G22" s="401"/>
       <c r="H22" s="393">
-        <v>1234567</v>
+        <v>1048985</v>
       </c>
       <c r="I22" s="393"/>
       <c r="J22" s="396">
@@ -29275,7 +29275,7 @@
     <row r="23" ht="24" customHeight="1" spans="2:13">
       <c r="B23" s="401"/>
       <c r="C23" s="393">
-        <v>1234567</v>
+        <v>1049874</v>
       </c>
       <c r="D23" s="393"/>
       <c r="E23" s="397">
@@ -29284,7 +29284,7 @@
       <c r="F23" s="393"/>
       <c r="G23" s="401"/>
       <c r="H23" s="393">
-        <v>1234567</v>
+        <v>1049867</v>
       </c>
       <c r="I23" s="393"/>
       <c r="J23" s="397">
@@ -29294,7 +29294,7 @@
     <row r="24" ht="24" customHeight="1" spans="2:13">
       <c r="B24" s="401"/>
       <c r="C24" s="393">
-        <v>1234567</v>
+        <v>1049872</v>
       </c>
       <c r="D24" s="393"/>
       <c r="E24" s="397">
@@ -29318,7 +29318,7 @@
       <c r="F25" s="393"/>
       <c r="G25" s="401"/>
       <c r="H25" s="393">
-        <v>1234567</v>
+        <v>1049874</v>
       </c>
       <c r="I25" s="393"/>
       <c r="J25" s="397">
@@ -32580,7 +32580,7 @@
       <c r="D6" s="286"/>
       <c r="E6" s="294" t="str">
         <f>'Gen Outb'!M18&amp;"/"&amp;'Gen Outb'!T18</f>
-        <v>南沙新港/示例国籍</v>
+        <v>南沙新港/中国香港</v>
       </c>
       <c r="F6" s="295"/>
       <c r="G6" s="295"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="D17" s="260" t="str">
         <f>'Gen Inb'!I10</f>
-        <v>IMO:1234567</v>
+        <v>IMO:1116648</v>
       </c>
       <c r="E17" s="255" t="s">
         <v>615</v>
@@ -35477,7 +35477,7 @@
         <v>635</v>
       </c>
       <c r="G26" s="259" t="str">
-        <f>IF(G25="示例船务代理有限公司","UNISCOGZ","")</f>
+        <f>IF(G25="广州联合国际船舶代理有限公司","UNISCOGZ","")</f>
         <v/>
       </c>
     </row>
@@ -35487,14 +35487,14 @@
       </c>
       <c r="D27" s="263" t="str">
         <f>'Gen Inb'!V12</f>
-        <v>联系人</v>
+        <v>白树辉</v>
       </c>
       <c r="E27" s="255" t="s">
         <v>637</v>
       </c>
       <c r="F27" s="268">
         <f>'Gen Inb'!V14</f>
-        <v>1234567</v>
+        <v>19120682489</v>
       </c>
       <c r="G27" s="268"/>
     </row>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="D17" s="260" t="str">
         <f>'Gen Inb'!I10</f>
-        <v>IMO:1234567</v>
+        <v>IMO:1116648</v>
       </c>
       <c r="E17" s="255" t="s">
         <v>615</v>
@@ -35764,7 +35764,7 @@
       </c>
       <c r="D21" s="256" t="str">
         <f>'Gen Outb'!W8</f>
-        <v>示例国籍</v>
+        <v>中国香港</v>
       </c>
       <c r="E21" s="255" t="s">
         <v>658</v>
@@ -35838,7 +35838,7 @@
         <v>635</v>
       </c>
       <c r="G26" s="259" t="str">
-        <f>IF(G25="示例船务代理有限公司","UNISCOGZ","")</f>
+        <f>IF(G25="广州联合国际船舶代理有限公司","UNISCOGZ","")</f>
         <v/>
       </c>
     </row>
@@ -35848,14 +35848,14 @@
       </c>
       <c r="D27" s="263" t="str">
         <f>'Gen Inb'!V12</f>
-        <v>联系人</v>
+        <v>白树辉</v>
       </c>
       <c r="E27" s="255" t="s">
         <v>637</v>
       </c>
       <c r="F27" s="268">
         <f>'Gen Inb'!V14</f>
-        <v>1234567</v>
+        <v>19120682489</v>
       </c>
       <c r="G27" s="268"/>
     </row>
@@ -36371,7 +36371,7 @@
       <c r="F4" s="162"/>
       <c r="J4" s="178" t="str">
         <f>'Parts A'!B5</f>
-        <v>IMO:1234567</v>
+        <v>IMO:9987574</v>
       </c>
       <c r="K4" s="178"/>
       <c r="L4" s="178"/>
@@ -36435,7 +36435,7 @@
       <c r="F9" s="178"/>
       <c r="G9" s="164" t="str">
         <f>'Gen Inb'!P12&amp;"："&amp;'Gen Inb'!V12</f>
-        <v>：联系人</v>
+        <v>：白树辉</v>
       </c>
       <c r="H9" s="164"/>
       <c r="I9" s="164"/>
@@ -36456,7 +36456,7 @@
       <c r="F10" s="176"/>
       <c r="G10" s="178" t="str">
         <f>'Gen Inb'!P14&amp;"  "&amp;'Gen Inb'!V14</f>
-        <v>13800000000  13800000000</v>
+        <v>39080621  19120682489</v>
       </c>
       <c r="H10" s="178"/>
       <c r="I10" s="178"/>
@@ -36668,7 +36668,7 @@
       <c r="F4" s="162"/>
       <c r="J4" s="178" t="str">
         <f>'IMO Gen Inb'!J4</f>
-        <v>IMO:1234567</v>
+        <v>IMO:9987574</v>
       </c>
       <c r="K4" s="178"/>
       <c r="L4" s="178"/>
@@ -36718,7 +36718,7 @@
       <c r="F7" s="164"/>
       <c r="J7" s="162" t="str">
         <f>'Gen Outb'!W8&amp;""&amp;'Gen Outb'!W9</f>
-        <v>示例国籍HONGKONG</v>
+        <v>中国香港HONGKONG</v>
       </c>
       <c r="K7" s="162"/>
       <c r="L7" s="162"/>
@@ -36732,7 +36732,7 @@
       <c r="F9" s="178"/>
       <c r="G9" s="164" t="str">
         <f>'Gen Inb'!P12&amp;"："&amp;'Gen Inb'!V12</f>
-        <v>：联系人</v>
+        <v>：白树辉</v>
       </c>
       <c r="H9" s="164"/>
       <c r="I9" s="164"/>
@@ -36753,7 +36753,7 @@
       <c r="F10" s="176"/>
       <c r="G10" s="178" t="str">
         <f>'Gen Inb'!P14&amp;"  "&amp;'Gen Inb'!V14</f>
-        <v>13800000000  13800000000</v>
+        <v>39080621  19120682489</v>
       </c>
       <c r="H10" s="178"/>
       <c r="I10" s="178"/>
@@ -36779,7 +36779,7 @@
     <row r="13" ht="47.25" customHeight="1" spans="2:12">
       <c r="B13" s="164" t="str">
         <f>'Gen Outb'!M18&amp;"  "&amp;"("&amp;'Gen Outb'!M19&amp;")"&amp;"——"&amp;'Gen Outb'!T18&amp;"  "&amp;"("&amp;'Gen Outb'!T19&amp;")"</f>
-        <v>南沙新港  (NANSHA NEW PORT)——示例国籍  (HONGKONG)</v>
+        <v>南沙新港  (NANSHA NEW PORT)——中国香港  (HONGKONG)</v>
       </c>
       <c r="C13" s="164"/>
       <c r="D13" s="164"/>
@@ -36954,7 +36954,7 @@
       <c r="D3" s="179"/>
       <c r="G3" s="177" t="str">
         <f>'IMO Gen Inb'!J4</f>
-        <v>IMO:1234567</v>
+        <v>IMO:9987574</v>
       </c>
       <c r="J3" s="177" t="str">
         <f>'IMO Gen Inb'!C5</f>
@@ -37020,13 +37020,13 @@
     <row r="23" customHeight="1" spans="4:10">
       <c r="D23" s="177" t="str">
         <f>'Gen Inb'!P12&amp;"："&amp;'Gen Inb'!V12</f>
-        <v>：联系人</v>
+        <v>：白树辉</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="4:10">
       <c r="D24" s="177" t="str">
         <f>'Gen Inb'!P14&amp;"，"&amp;'Gen Inb'!V14</f>
-        <v>13800000000，13800000000</v>
+        <v>39080621，19120682489</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="4:10">
@@ -37088,7 +37088,7 @@
       <c r="D3" s="179"/>
       <c r="G3" s="178" t="str">
         <f>'IMO Gen Outb'!J4</f>
-        <v>IMO:1234567</v>
+        <v>IMO:9987574</v>
       </c>
       <c r="J3" s="177" t="str">
         <f>'IMO Gen Outb'!C5</f>
@@ -37116,7 +37116,7 @@
       </c>
       <c r="H5" s="162" t="str">
         <f>'IMO Gen Outb'!J7</f>
-        <v>示例国籍HONGKONG</v>
+        <v>中国香港HONGKONG</v>
       </c>
       <c r="I5" s="162"/>
       <c r="J5" s="162"/>
@@ -37154,13 +37154,13 @@
     <row r="23" customHeight="1" spans="4:13">
       <c r="D23" s="177" t="str">
         <f>'Gen Inb'!P12&amp;"："&amp;'Gen Inb'!V12</f>
-        <v>：联系人</v>
+        <v>：白树辉</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="4:13">
       <c r="D24" s="177" t="str">
         <f>'Gen Inb'!P14&amp;"，"&amp;'Gen Inb'!V14</f>
-        <v>13800000000，13800000000</v>
+        <v>39080621，19120682489</v>
       </c>
       <c r="M24" s="177" t="s">
         <v>684</v>
@@ -37234,7 +37234,7 @@
       <c r="G4" s="163"/>
       <c r="H4" s="164" t="str">
         <f>'IMO Gen Inb'!J4</f>
-        <v>IMO:1234567</v>
+        <v>IMO:9987574</v>
       </c>
       <c r="L4" s="164" t="str">
         <f>'IMO Gen Inb'!C5</f>
@@ -37313,7 +37313,7 @@
       </c>
       <c r="K8" s="1219" t="str">
         <f>IF('Crew Inb'!K11&lt;&gt;"",'Crew Inb'!K11,"")</f>
-        <v>TEST0001</v>
+        <v>B42BR8005</v>
       </c>
       <c r="L8" s="166"/>
     </row>
@@ -37352,7 +37352,7 @@
       </c>
       <c r="K9" s="166" t="str">
         <f>IF('Crew Inb'!K12&lt;&gt;"",'Crew Inb'!K12,"")</f>
-        <v>TEST0002</v>
+        <v>AB498691</v>
       </c>
       <c r="L9" s="166"/>
     </row>
@@ -37391,7 +37391,7 @@
       </c>
       <c r="K10" s="166" t="str">
         <f>IF('Crew Inb'!K13&lt;&gt;"",'Crew Inb'!K13,"")</f>
-        <v>TEST0003</v>
+        <v>P0392496A</v>
       </c>
       <c r="L10" s="166"/>
     </row>
@@ -37402,7 +37402,7 @@
       </c>
       <c r="C11" s="167" t="str">
         <f>IF('Crew Inb'!C14&lt;&gt;"",'Crew Inb'!C14&amp;" "&amp;'Crew Inb'!D14,"")</f>
-        <v>赵六 </v>
+        <v>GONZAGA JOHN BRIAN CANALITA </v>
       </c>
       <c r="D11" s="166" t="str">
         <f>IF('Crew Inb'!E14&lt;&gt;"",'Crew Inb'!E14,"")</f>
@@ -37430,7 +37430,7 @@
       </c>
       <c r="K11" s="166" t="str">
         <f>IF('Crew Inb'!K14&lt;&gt;"",'Crew Inb'!K14,"")</f>
-        <v>TEST0004</v>
+        <v>EC3697674</v>
       </c>
       <c r="L11" s="166"/>
     </row>
@@ -37441,7 +37441,7 @@
       </c>
       <c r="C12" s="167" t="str">
         <f>IF('Crew Inb'!C15&lt;&gt;"",'Crew Inb'!C15&amp;" "&amp;'Crew Inb'!D15,"")</f>
-        <v>钱七 </v>
+        <v>DYACHENKO VASYL </v>
       </c>
       <c r="D12" s="166" t="str">
         <f>IF('Crew Inb'!E15&lt;&gt;"",'Crew Inb'!E15,"")</f>
@@ -37469,7 +37469,7 @@
       </c>
       <c r="K12" s="166" t="str">
         <f>IF('Crew Inb'!K15&lt;&gt;"",'Crew Inb'!K15,"")</f>
-        <v>TEST0005</v>
+        <v>AB406216</v>
       </c>
       <c r="L12" s="166"/>
     </row>
@@ -37480,7 +37480,7 @@
       </c>
       <c r="C13" s="167" t="str">
         <f>IF('Crew Inb'!C16&lt;&gt;"",'Crew Inb'!C16&amp;" "&amp;'Crew Inb'!D16,"")</f>
-        <v>孙八 </v>
+        <v>BALAKIN OLEG </v>
       </c>
       <c r="D13" s="166" t="str">
         <f>IF('Crew Inb'!E16&lt;&gt;"",'Crew Inb'!E16,"")</f>
@@ -37508,7 +37508,7 @@
       </c>
       <c r="K13" s="166" t="str">
         <f>IF('Crew Inb'!K16&lt;&gt;"",'Crew Inb'!K16,"")</f>
-        <v>TEST0006</v>
+        <v>AB565162</v>
       </c>
       <c r="L13" s="166"/>
     </row>
@@ -37519,7 +37519,7 @@
       </c>
       <c r="C14" s="167" t="str">
         <f>IF('Crew Inb'!C17&lt;&gt;"",'Crew Inb'!C17&amp;" "&amp;'Crew Inb'!D17,"")</f>
-        <v>周九 </v>
+        <v>BACERDO OMAR DAMES </v>
       </c>
       <c r="D14" s="166" t="str">
         <f>IF('Crew Inb'!E17&lt;&gt;"",'Crew Inb'!E17,"")</f>
@@ -37547,7 +37547,7 @@
       </c>
       <c r="K14" s="166" t="str">
         <f>IF('Crew Inb'!K17&lt;&gt;"",'Crew Inb'!K17,"")</f>
-        <v>TEST0007</v>
+        <v>P1649209A</v>
       </c>
       <c r="L14" s="166"/>
     </row>
@@ -37558,7 +37558,7 @@
       </c>
       <c r="C15" s="167" t="str">
         <f>IF('Crew Inb'!C18&lt;&gt;"",'Crew Inb'!C18&amp;" "&amp;'Crew Inb'!D18,"")</f>
-        <v>吴十 </v>
+        <v>SANTACERA ROTSEN MAR DAYADAY </v>
       </c>
       <c r="D15" s="166" t="str">
         <f>IF('Crew Inb'!E18&lt;&gt;"",'Crew Inb'!E18,"")</f>
@@ -37586,7 +37586,7 @@
       </c>
       <c r="K15" s="166" t="str">
         <f>IF('Crew Inb'!K18&lt;&gt;"",'Crew Inb'!K18,"")</f>
-        <v>TEST0008</v>
+        <v>P1399821A</v>
       </c>
       <c r="L15" s="166"/>
     </row>
@@ -37597,7 +37597,7 @@
       </c>
       <c r="C16" s="167" t="str">
         <f>IF('Crew Inb'!C19&lt;&gt;"",'Crew Inb'!C19&amp;" "&amp;'Crew Inb'!D19,"")</f>
-        <v>郑一 </v>
+        <v>JAVIER EDGAR AMMEN </v>
       </c>
       <c r="D16" s="166" t="str">
         <f>IF('Crew Inb'!E19&lt;&gt;"",'Crew Inb'!E19,"")</f>
@@ -37625,7 +37625,7 @@
       </c>
       <c r="K16" s="166" t="str">
         <f>IF('Crew Inb'!K19&lt;&gt;"",'Crew Inb'!K19,"")</f>
-        <v>TEST0009</v>
+        <v>EC4641553</v>
       </c>
       <c r="L16" s="166"/>
     </row>
@@ -37636,7 +37636,7 @@
       </c>
       <c r="C17" s="167" t="str">
         <f>IF('Crew Inb'!C20&lt;&gt;"",'Crew Inb'!C20&amp;" "&amp;'Crew Inb'!D20,"")</f>
-        <v>王一 </v>
+        <v>ELPA KENNETH BLANCO </v>
       </c>
       <c r="D17" s="166" t="str">
         <f>IF('Crew Inb'!E20&lt;&gt;"",'Crew Inb'!E20,"")</f>
@@ -37664,7 +37664,7 @@
       </c>
       <c r="K17" s="166" t="str">
         <f>IF('Crew Inb'!K20&lt;&gt;"",'Crew Inb'!K20,"")</f>
-        <v>TEST0010</v>
+        <v>P2512380A</v>
       </c>
       <c r="L17" s="166"/>
     </row>
@@ -37675,7 +37675,7 @@
       </c>
       <c r="C18" s="167" t="str">
         <f>IF('Crew Inb'!C21&lt;&gt;"",'Crew Inb'!C21&amp;" "&amp;'Crew Inb'!D21,"")</f>
-        <v>李一 </v>
+        <v>FLORENTINO JOEMARIE LACHICA </v>
       </c>
       <c r="D18" s="166" t="str">
         <f>IF('Crew Inb'!E21&lt;&gt;"",'Crew Inb'!E21,"")</f>
@@ -37703,7 +37703,7 @@
       </c>
       <c r="K18" s="166" t="str">
         <f>IF('Crew Inb'!K21&lt;&gt;"",'Crew Inb'!K21,"")</f>
-        <v>TEST0011</v>
+        <v>EC6525043</v>
       </c>
       <c r="L18" s="166"/>
     </row>
@@ -37714,7 +37714,7 @@
       </c>
       <c r="C19" s="167" t="str">
         <f>IF('Crew Inb'!C22&lt;&gt;"",'Crew Inb'!C22&amp;" "&amp;'Crew Inb'!D22,"")</f>
-        <v>赵一 </v>
+        <v>SUAREZ JETTE ANTHONY CAPANAS </v>
       </c>
       <c r="D19" s="166" t="str">
         <f>IF('Crew Inb'!E22&lt;&gt;"",'Crew Inb'!E22,"")</f>
@@ -37742,7 +37742,7 @@
       </c>
       <c r="K19" s="166" t="str">
         <f>IF('Crew Inb'!K22&lt;&gt;"",'Crew Inb'!K22,"")</f>
-        <v>TEST0012</v>
+        <v>P0863919A</v>
       </c>
       <c r="L19" s="166"/>
     </row>
@@ -37753,7 +37753,7 @@
       </c>
       <c r="C20" s="167" t="str">
         <f>IF('Crew Inb'!C23&lt;&gt;"",'Crew Inb'!C23&amp;" "&amp;'Crew Inb'!D23,"")</f>
-        <v>陈一 </v>
+        <v>JAMERO IANJAY HAMOAY </v>
       </c>
       <c r="D20" s="166" t="str">
         <f>IF('Crew Inb'!E23&lt;&gt;"",'Crew Inb'!E23,"")</f>
@@ -37781,7 +37781,7 @@
       </c>
       <c r="K20" s="166" t="str">
         <f>IF('Crew Inb'!K23&lt;&gt;"",'Crew Inb'!K23,"")</f>
-        <v>TEST0013</v>
+        <v>EC5956980</v>
       </c>
       <c r="L20" s="166"/>
     </row>
@@ -37792,7 +37792,7 @@
       </c>
       <c r="C21" s="167" t="str">
         <f>IF('Crew Inb'!C24&lt;&gt;"",'Crew Inb'!C24&amp;" "&amp;'Crew Inb'!D24,"")</f>
-        <v>刘一 </v>
+        <v>PELLETERO ALLEN SEGISMUNDO </v>
       </c>
       <c r="D21" s="166" t="str">
         <f>IF('Crew Inb'!E24&lt;&gt;"",'Crew Inb'!E24,"")</f>
@@ -37820,7 +37820,7 @@
       </c>
       <c r="K21" s="166" t="str">
         <f>IF('Crew Inb'!K24&lt;&gt;"",'Crew Inb'!K24,"")</f>
-        <v>TEST0014</v>
+        <v>P3925249A</v>
       </c>
       <c r="L21" s="166"/>
     </row>
@@ -37831,7 +37831,7 @@
       </c>
       <c r="C22" s="167" t="str">
         <f>IF('Crew Inb'!C25&lt;&gt;"",'Crew Inb'!C25&amp;" "&amp;'Crew Inb'!D25,"")</f>
-        <v>杨一 </v>
+        <v>OLOJAN ROSEN JUANICO </v>
       </c>
       <c r="D22" s="166" t="str">
         <f>IF('Crew Inb'!E25&lt;&gt;"",'Crew Inb'!E25,"")</f>
@@ -37859,7 +37859,7 @@
       </c>
       <c r="K22" s="166" t="str">
         <f>IF('Crew Inb'!K25&lt;&gt;"",'Crew Inb'!K25,"")</f>
-        <v>TEST0015</v>
+        <v>EC4389049</v>
       </c>
       <c r="L22" s="166"/>
     </row>
@@ -37870,7 +37870,7 @@
       </c>
       <c r="C23" s="167" t="str">
         <f>IF('Crew Inb'!C26&lt;&gt;"",'Crew Inb'!C26&amp;" "&amp;'Crew Inb'!D26,"")</f>
-        <v>黄一 </v>
+        <v>CAMILOTE GEOFFREY CALETINA </v>
       </c>
       <c r="D23" s="166" t="str">
         <f>IF('Crew Inb'!E26&lt;&gt;"",'Crew Inb'!E26,"")</f>
@@ -37898,7 +37898,7 @@
       </c>
       <c r="K23" s="166" t="str">
         <f>IF('Crew Inb'!K26&lt;&gt;"",'Crew Inb'!K26,"")</f>
-        <v>TEST0016</v>
+        <v>P2263420A</v>
       </c>
       <c r="L23" s="166"/>
     </row>
@@ -37909,7 +37909,7 @@
       </c>
       <c r="C24" s="167" t="str">
         <f>IF('Crew Inb'!C27&lt;&gt;"",'Crew Inb'!C27&amp;" "&amp;'Crew Inb'!D27,"")</f>
-        <v>周一 </v>
+        <v>ECAT JOSEPH PAUL TENEBRO </v>
       </c>
       <c r="D24" s="166" t="str">
         <f>IF('Crew Inb'!E27&lt;&gt;"",'Crew Inb'!E27,"")</f>
@@ -37937,7 +37937,7 @@
       </c>
       <c r="K24" s="166" t="str">
         <f>IF('Crew Inb'!K27&lt;&gt;"",'Crew Inb'!K27,"")</f>
-        <v>TEST0017</v>
+        <v>P3596511A</v>
       </c>
       <c r="L24" s="166"/>
     </row>
@@ -37948,7 +37948,7 @@
       </c>
       <c r="C25" s="167" t="str">
         <f>IF('Crew Inb'!C28&lt;&gt;"",'Crew Inb'!C28&amp;" "&amp;'Crew Inb'!D28,"")</f>
-        <v>吴一 </v>
+        <v>DELIS  EUGENE SALIGUMBA </v>
       </c>
       <c r="D25" s="166" t="str">
         <f>IF('Crew Inb'!E28&lt;&gt;"",'Crew Inb'!E28,"")</f>
@@ -37976,7 +37976,7 @@
       </c>
       <c r="K25" s="166" t="str">
         <f>IF('Crew Inb'!K28&lt;&gt;"",'Crew Inb'!K28,"")</f>
-        <v>TEST0018</v>
+        <v>EC5270716</v>
       </c>
       <c r="L25" s="166"/>
     </row>
@@ -37987,7 +37987,7 @@
       </c>
       <c r="C26" s="167" t="str">
         <f>IF('Crew Inb'!C29&lt;&gt;"",'Crew Inb'!C29&amp;" "&amp;'Crew Inb'!D29,"")</f>
-        <v>徐一 </v>
+        <v>MOGRO ROMELITO LOSTE </v>
       </c>
       <c r="D26" s="166" t="str">
         <f>IF('Crew Inb'!E29&lt;&gt;"",'Crew Inb'!E29,"")</f>
@@ -38015,7 +38015,7 @@
       </c>
       <c r="K26" s="166" t="str">
         <f>IF('Crew Inb'!K29&lt;&gt;"",'Crew Inb'!K29,"")</f>
-        <v>TEST0019</v>
+        <v>EC2844651</v>
       </c>
       <c r="L26" s="166"/>
     </row>
@@ -38085,7 +38085,7 @@
       <c r="G31" s="163"/>
       <c r="H31" s="164" t="str">
         <f>'IMO Gen Inb'!J4</f>
-        <v>IMO:1234567</v>
+        <v>IMO:9987574</v>
       </c>
       <c r="I31" s="163"/>
       <c r="J31" s="163"/>
@@ -38140,7 +38140,7 @@
       </c>
       <c r="C35" s="167" t="str">
         <f>IF('Crew Inb'!C30&lt;&gt;"",'Crew Inb'!C30&amp;" "&amp;'Crew Inb'!D30,"")</f>
-        <v>孙一 </v>
+        <v>CAMANAY JONATHAN SUAZO </v>
       </c>
       <c r="D35" s="166" t="s">
         <v>232</v>
@@ -38167,7 +38167,7 @@
       </c>
       <c r="K35" s="166" t="str">
         <f>IF('Crew Inb'!K30&lt;&gt;"",'Crew Inb'!K30,"")</f>
-        <v>TEST0020</v>
+        <v>EC8290337</v>
       </c>
       <c r="L35" s="166"/>
     </row>
@@ -38526,7 +38526,7 @@
       <c r="G4" s="163"/>
       <c r="H4" s="164" t="str">
         <f>'IMO Gen Outb'!J4</f>
-        <v>IMO:1234567</v>
+        <v>IMO:9987574</v>
       </c>
       <c r="L4" s="164" t="str">
         <f>'IMO Gen Outb'!C5</f>
@@ -38563,7 +38563,7 @@
       <c r="G6" s="163"/>
       <c r="I6" s="162" t="str">
         <f>'IMO Gen Outb'!J7</f>
-        <v>示例国籍HONGKONG</v>
+        <v>中国香港HONGKONG</v>
       </c>
       <c r="J6" s="162"/>
       <c r="K6" s="162"/>
@@ -38605,7 +38605,7 @@
       </c>
       <c r="K8" s="1219" t="str">
         <f>IF('Crew Inb'!K11&lt;&gt;"",'Crew Inb'!K11,"")</f>
-        <v>TEST0001</v>
+        <v>B42BR8005</v>
       </c>
       <c r="L8" s="166"/>
     </row>
@@ -38644,7 +38644,7 @@
       </c>
       <c r="K9" s="166" t="str">
         <f>IF('Crew Inb'!K12&lt;&gt;"",'Crew Inb'!K12,"")</f>
-        <v>TEST0002</v>
+        <v>AB498691</v>
       </c>
       <c r="L9" s="166"/>
     </row>
@@ -38683,7 +38683,7 @@
       </c>
       <c r="K10" s="166" t="str">
         <f>IF('Crew Inb'!K13&lt;&gt;"",'Crew Inb'!K13,"")</f>
-        <v>TEST0003</v>
+        <v>P0392496A</v>
       </c>
       <c r="L10" s="166"/>
     </row>
@@ -38694,7 +38694,7 @@
       </c>
       <c r="C11" s="167" t="str">
         <f>IF('Crew Inb'!C14&lt;&gt;"",'Crew Inb'!C14&amp;" "&amp;'Crew Inb'!D14,"")</f>
-        <v>赵六 </v>
+        <v>GONZAGA JOHN BRIAN CANALITA </v>
       </c>
       <c r="D11" s="166" t="str">
         <f>IF('Crew Inb'!E14&lt;&gt;"",'Crew Inb'!E14,"")</f>
@@ -38722,7 +38722,7 @@
       </c>
       <c r="K11" s="166" t="str">
         <f>IF('Crew Inb'!K14&lt;&gt;"",'Crew Inb'!K14,"")</f>
-        <v>TEST0004</v>
+        <v>EC3697674</v>
       </c>
       <c r="L11" s="166"/>
     </row>
@@ -38733,7 +38733,7 @@
       </c>
       <c r="C12" s="167" t="str">
         <f>IF('Crew Inb'!C15&lt;&gt;"",'Crew Inb'!C15&amp;" "&amp;'Crew Inb'!D15,"")</f>
-        <v>钱七 </v>
+        <v>DYACHENKO VASYL </v>
       </c>
       <c r="D12" s="166" t="str">
         <f>IF('Crew Inb'!E15&lt;&gt;"",'Crew Inb'!E15,"")</f>
@@ -38761,7 +38761,7 @@
       </c>
       <c r="K12" s="166" t="str">
         <f>IF('Crew Inb'!K15&lt;&gt;"",'Crew Inb'!K15,"")</f>
-        <v>TEST0005</v>
+        <v>AB406216</v>
       </c>
       <c r="L12" s="166"/>
     </row>
@@ -38772,7 +38772,7 @@
       </c>
       <c r="C13" s="167" t="str">
         <f>IF('Crew Inb'!C16&lt;&gt;"",'Crew Inb'!C16&amp;" "&amp;'Crew Inb'!D16,"")</f>
-        <v>孙八 </v>
+        <v>BALAKIN OLEG </v>
       </c>
       <c r="D13" s="166" t="str">
         <f>IF('Crew Inb'!E16&lt;&gt;"",'Crew Inb'!E16,"")</f>
@@ -38800,7 +38800,7 @@
       </c>
       <c r="K13" s="166" t="str">
         <f>IF('Crew Inb'!K16&lt;&gt;"",'Crew Inb'!K16,"")</f>
-        <v>TEST0006</v>
+        <v>AB565162</v>
       </c>
       <c r="L13" s="166"/>
     </row>
@@ -38811,7 +38811,7 @@
       </c>
       <c r="C14" s="167" t="str">
         <f>IF('Crew Inb'!C17&lt;&gt;"",'Crew Inb'!C17&amp;" "&amp;'Crew Inb'!D17,"")</f>
-        <v>周九 </v>
+        <v>BACERDO OMAR DAMES </v>
       </c>
       <c r="D14" s="166" t="str">
         <f>IF('Crew Inb'!E17&lt;&gt;"",'Crew Inb'!E17,"")</f>
@@ -38839,7 +38839,7 @@
       </c>
       <c r="K14" s="166" t="str">
         <f>IF('Crew Inb'!K17&lt;&gt;"",'Crew Inb'!K17,"")</f>
-        <v>TEST0007</v>
+        <v>P1649209A</v>
       </c>
       <c r="L14" s="166"/>
     </row>
@@ -38850,7 +38850,7 @@
       </c>
       <c r="C15" s="167" t="str">
         <f>IF('Crew Inb'!C18&lt;&gt;"",'Crew Inb'!C18&amp;" "&amp;'Crew Inb'!D18,"")</f>
-        <v>吴十 </v>
+        <v>SANTACERA ROTSEN MAR DAYADAY </v>
       </c>
       <c r="D15" s="166" t="str">
         <f>IF('Crew Inb'!E18&lt;&gt;"",'Crew Inb'!E18,"")</f>
@@ -38878,7 +38878,7 @@
       </c>
       <c r="K15" s="166" t="str">
         <f>IF('Crew Inb'!K18&lt;&gt;"",'Crew Inb'!K18,"")</f>
-        <v>TEST0008</v>
+        <v>P1399821A</v>
       </c>
       <c r="L15" s="166"/>
     </row>
@@ -38889,7 +38889,7 @@
       </c>
       <c r="C16" s="167" t="str">
         <f>IF('Crew Inb'!C19&lt;&gt;"",'Crew Inb'!C19&amp;" "&amp;'Crew Inb'!D19,"")</f>
-        <v>郑一 </v>
+        <v>JAVIER EDGAR AMMEN </v>
       </c>
       <c r="D16" s="166" t="str">
         <f>IF('Crew Inb'!E19&lt;&gt;"",'Crew Inb'!E19,"")</f>
@@ -38917,7 +38917,7 @@
       </c>
       <c r="K16" s="166" t="str">
         <f>IF('Crew Inb'!K19&lt;&gt;"",'Crew Inb'!K19,"")</f>
-        <v>TEST0009</v>
+        <v>EC4641553</v>
       </c>
       <c r="L16" s="166"/>
     </row>
@@ -38928,7 +38928,7 @@
       </c>
       <c r="C17" s="167" t="str">
         <f>IF('Crew Inb'!C20&lt;&gt;"",'Crew Inb'!C20&amp;" "&amp;'Crew Inb'!D20,"")</f>
-        <v>王一 </v>
+        <v>ELPA KENNETH BLANCO </v>
       </c>
       <c r="D17" s="166" t="str">
         <f>IF('Crew Inb'!E20&lt;&gt;"",'Crew Inb'!E20,"")</f>
@@ -38956,7 +38956,7 @@
       </c>
       <c r="K17" s="166" t="str">
         <f>IF('Crew Inb'!K20&lt;&gt;"",'Crew Inb'!K20,"")</f>
-        <v>TEST0010</v>
+        <v>P2512380A</v>
       </c>
       <c r="L17" s="166"/>
     </row>
@@ -38967,7 +38967,7 @@
       </c>
       <c r="C18" s="167" t="str">
         <f>IF('Crew Inb'!C21&lt;&gt;"",'Crew Inb'!C21&amp;" "&amp;'Crew Inb'!D21,"")</f>
-        <v>李一 </v>
+        <v>FLORENTINO JOEMARIE LACHICA </v>
       </c>
       <c r="D18" s="166" t="str">
         <f>IF('Crew Inb'!E21&lt;&gt;"",'Crew Inb'!E21,"")</f>
@@ -38995,7 +38995,7 @@
       </c>
       <c r="K18" s="166" t="str">
         <f>IF('Crew Inb'!K21&lt;&gt;"",'Crew Inb'!K21,"")</f>
-        <v>TEST0011</v>
+        <v>EC6525043</v>
       </c>
       <c r="L18" s="166"/>
     </row>
@@ -39006,7 +39006,7 @@
       </c>
       <c r="C19" s="167" t="str">
         <f>IF('Crew Inb'!C22&lt;&gt;"",'Crew Inb'!C22&amp;" "&amp;'Crew Inb'!D22,"")</f>
-        <v>赵一 </v>
+        <v>SUAREZ JETTE ANTHONY CAPANAS </v>
       </c>
       <c r="D19" s="166" t="str">
         <f>IF('Crew Inb'!E22&lt;&gt;"",'Crew Inb'!E22,"")</f>
@@ -39034,7 +39034,7 @@
       </c>
       <c r="K19" s="166" t="str">
         <f>IF('Crew Inb'!K22&lt;&gt;"",'Crew Inb'!K22,"")</f>
-        <v>TEST0012</v>
+        <v>P0863919A</v>
       </c>
       <c r="L19" s="166"/>
     </row>
@@ -39045,7 +39045,7 @@
       </c>
       <c r="C20" s="167" t="str">
         <f>IF('Crew Inb'!C23&lt;&gt;"",'Crew Inb'!C23&amp;" "&amp;'Crew Inb'!D23,"")</f>
-        <v>陈一 </v>
+        <v>JAMERO IANJAY HAMOAY </v>
       </c>
       <c r="D20" s="166" t="str">
         <f>IF('Crew Inb'!E23&lt;&gt;"",'Crew Inb'!E23,"")</f>
@@ -39073,7 +39073,7 @@
       </c>
       <c r="K20" s="166" t="str">
         <f>IF('Crew Inb'!K23&lt;&gt;"",'Crew Inb'!K23,"")</f>
-        <v>TEST0013</v>
+        <v>EC5956980</v>
       </c>
       <c r="L20" s="166"/>
     </row>
@@ -39084,7 +39084,7 @@
       </c>
       <c r="C21" s="167" t="str">
         <f>IF('Crew Inb'!C24&lt;&gt;"",'Crew Inb'!C24&amp;" "&amp;'Crew Inb'!D24,"")</f>
-        <v>刘一 </v>
+        <v>PELLETERO ALLEN SEGISMUNDO </v>
       </c>
       <c r="D21" s="166" t="str">
         <f>IF('Crew Inb'!E24&lt;&gt;"",'Crew Inb'!E24,"")</f>
@@ -39112,7 +39112,7 @@
       </c>
       <c r="K21" s="166" t="str">
         <f>IF('Crew Inb'!K24&lt;&gt;"",'Crew Inb'!K24,"")</f>
-        <v>TEST0014</v>
+        <v>P3925249A</v>
       </c>
       <c r="L21" s="166"/>
     </row>
@@ -39123,7 +39123,7 @@
       </c>
       <c r="C22" s="167" t="str">
         <f>IF('Crew Inb'!C25&lt;&gt;"",'Crew Inb'!C25&amp;" "&amp;'Crew Inb'!D25,"")</f>
-        <v>杨一 </v>
+        <v>OLOJAN ROSEN JUANICO </v>
       </c>
       <c r="D22" s="166" t="str">
         <f>IF('Crew Inb'!E25&lt;&gt;"",'Crew Inb'!E25,"")</f>
@@ -39151,7 +39151,7 @@
       </c>
       <c r="K22" s="166" t="str">
         <f>IF('Crew Inb'!K25&lt;&gt;"",'Crew Inb'!K25,"")</f>
-        <v>TEST0015</v>
+        <v>EC4389049</v>
       </c>
       <c r="L22" s="166"/>
     </row>
@@ -39162,7 +39162,7 @@
       </c>
       <c r="C23" s="167" t="str">
         <f>IF('Crew Inb'!C26&lt;&gt;"",'Crew Inb'!C26&amp;" "&amp;'Crew Inb'!D26,"")</f>
-        <v>黄一 </v>
+        <v>CAMILOTE GEOFFREY CALETINA </v>
       </c>
       <c r="D23" s="166" t="str">
         <f>IF('Crew Inb'!E26&lt;&gt;"",'Crew Inb'!E26,"")</f>
@@ -39190,7 +39190,7 @@
       </c>
       <c r="K23" s="166" t="str">
         <f>IF('Crew Inb'!K26&lt;&gt;"",'Crew Inb'!K26,"")</f>
-        <v>TEST0016</v>
+        <v>P2263420A</v>
       </c>
       <c r="L23" s="166"/>
     </row>
@@ -39201,7 +39201,7 @@
       </c>
       <c r="C24" s="167" t="str">
         <f>IF('Crew Inb'!C27&lt;&gt;"",'Crew Inb'!C27&amp;" "&amp;'Crew Inb'!D27,"")</f>
-        <v>周一 </v>
+        <v>ECAT JOSEPH PAUL TENEBRO </v>
       </c>
       <c r="D24" s="166" t="str">
         <f>IF('Crew Inb'!E27&lt;&gt;"",'Crew Inb'!E27,"")</f>
@@ -39229,7 +39229,7 @@
       </c>
       <c r="K24" s="166" t="str">
         <f>IF('Crew Inb'!K27&lt;&gt;"",'Crew Inb'!K27,"")</f>
-        <v>TEST0017</v>
+        <v>P3596511A</v>
       </c>
       <c r="L24" s="166"/>
     </row>
@@ -39240,7 +39240,7 @@
       </c>
       <c r="C25" s="167" t="str">
         <f>IF('Crew Inb'!C28&lt;&gt;"",'Crew Inb'!C28&amp;" "&amp;'Crew Inb'!D28,"")</f>
-        <v>吴一 </v>
+        <v>DELIS  EUGENE SALIGUMBA </v>
       </c>
       <c r="D25" s="166" t="str">
         <f>IF('Crew Inb'!E28&lt;&gt;"",'Crew Inb'!E28,"")</f>
@@ -39268,7 +39268,7 @@
       </c>
       <c r="K25" s="166" t="str">
         <f>IF('Crew Inb'!K28&lt;&gt;"",'Crew Inb'!K28,"")</f>
-        <v>TEST0018</v>
+        <v>EC5270716</v>
       </c>
       <c r="L25" s="166"/>
     </row>
@@ -39279,7 +39279,7 @@
       </c>
       <c r="C26" s="167" t="str">
         <f>IF('Crew Inb'!C29&lt;&gt;"",'Crew Inb'!C29&amp;" "&amp;'Crew Inb'!D29,"")</f>
-        <v>徐一 </v>
+        <v>MOGRO ROMELITO LOSTE </v>
       </c>
       <c r="D26" s="166" t="str">
         <f>IF('Crew Inb'!E29&lt;&gt;"",'Crew Inb'!E29,"")</f>
@@ -39307,7 +39307,7 @@
       </c>
       <c r="K26" s="166" t="str">
         <f>IF('Crew Inb'!K29&lt;&gt;"",'Crew Inb'!K29,"")</f>
-        <v>TEST0019</v>
+        <v>EC2844651</v>
       </c>
       <c r="L26" s="166"/>
     </row>
@@ -39348,7 +39348,7 @@
       <c r="G31" s="163"/>
       <c r="H31" s="164" t="str">
         <f>'IMO Gen Outb'!J4</f>
-        <v>IMO:1234567</v>
+        <v>IMO:9987574</v>
       </c>
       <c r="I31" s="163"/>
       <c r="J31" s="163"/>
@@ -39390,7 +39390,7 @@
       <c r="H33" s="163"/>
       <c r="I33" s="162" t="str">
         <f>'IMO Gen Outb'!J7</f>
-        <v>示例国籍HONGKONG</v>
+        <v>中国香港HONGKONG</v>
       </c>
       <c r="J33" s="162"/>
       <c r="K33" s="162"/>
@@ -39403,7 +39403,7 @@
       </c>
       <c r="C35" s="167" t="str">
         <f>IF('Crew Inb'!C30&lt;&gt;"",'Crew Inb'!C30&amp;" "&amp;'Crew Inb'!D30,"")</f>
-        <v>孙一 </v>
+        <v>CAMANAY JONATHAN SUAZO </v>
       </c>
       <c r="D35" s="166" t="s">
         <v>232</v>
@@ -39427,7 +39427,7 @@
       </c>
       <c r="K35" s="166" t="str">
         <f>IF('Crew Inb'!K30&lt;&gt;"",'Crew Inb'!K30,"")</f>
-        <v>TEST0020</v>
+        <v>EC8290337</v>
       </c>
       <c r="L35" s="166"/>
     </row>
@@ -39814,7 +39814,7 @@
       </c>
       <c r="H5" s="1134" t="str">
         <f>'Gen Outb'!W8</f>
-        <v>示例国籍</v>
+        <v>中国香港</v>
       </c>
       <c r="I5" s="1137"/>
       <c r="J5" s="1131"/>
@@ -40470,7 +40470,7 @@
       </c>
       <c r="B4" s="103"/>
       <c r="C4" s="104">
-        <v>1234567</v>
+        <v>9790074</v>
       </c>
       <c r="D4" s="104"/>
       <c r="E4" s="104"/>
@@ -41464,7 +41464,7 @@
       </c>
       <c r="H15" s="86" t="str">
         <f>'Gen Outb'!W8</f>
-        <v>示例国籍</v>
+        <v>中国香港</v>
       </c>
       <c r="I15" s="86"/>
       <c r="J15" s="86"/>
@@ -41550,7 +41550,7 @@
       </c>
       <c r="D30" s="68">
         <f>'Gen Inb'!R27</f>
-        <v>1234567</v>
+        <v>352005840</v>
       </c>
     </row>
     <row r="32" spans="3:8">
@@ -41603,7 +41603,7 @@
       <c r="H46" s="62"/>
       <c r="M46" s="76" t="str">
         <f>'Gen Inb'!V12&amp;"  "&amp;'Gen Inb'!V14</f>
-        <v>联系人  13800000000</v>
+        <v>白树辉  19120682489</v>
       </c>
     </row>
     <row r="48" spans="3:13">
@@ -41817,7 +41817,7 @@
       <c r="G18" s="65"/>
       <c r="H18" s="80" t="str">
         <f>'Gen Outb'!W8</f>
-        <v>示例国籍</v>
+        <v>中国香港</v>
       </c>
       <c r="I18" s="80"/>
       <c r="J18" s="80"/>
@@ -41848,7 +41848,7 @@
       <c r="H28" s="62"/>
       <c r="M28" s="76" t="str">
         <f>'Gen Inb'!V12&amp;"  "&amp;'Gen Inb'!V14</f>
-        <v>联系人  13800000000</v>
+        <v>白树辉  19120682489</v>
       </c>
     </row>
     <row r="30" spans="3:13">
@@ -42024,7 +42024,7 @@
       </c>
       <c r="H15" s="64" t="str">
         <f>'Gen Outb'!W8</f>
-        <v>示例国籍</v>
+        <v>中国香港</v>
       </c>
       <c r="I15" s="64"/>
       <c r="J15" s="64"/>
@@ -42158,7 +42158,7 @@
       <c r="H46" s="62"/>
       <c r="M46" s="76" t="str">
         <f>'Gen Inb'!V12&amp;"  "&amp;'Gen Inb'!V14</f>
-        <v>联系人  13800000000</v>
+        <v>白树辉  19120682489</v>
       </c>
     </row>
     <row r="48" spans="4:13">
@@ -43479,7 +43479,7 @@
       </c>
       <c r="E3" s="7" t="str">
         <f>'Parts A'!B5</f>
-        <v>IMO:1234567</v>
+        <v>IMO:9987574</v>
       </c>
       <c r="F3" s="8"/>
     </row>
@@ -44774,7 +44774,7 @@
       <c r="N14" s="932"/>
       <c r="O14" s="933"/>
       <c r="P14" s="934">
-        <v>1234567</v>
+        <v>39080621</v>
       </c>
       <c r="Q14" s="935"/>
       <c r="R14" s="935"/>
@@ -44782,7 +44782,7 @@
       <c r="T14" s="935"/>
       <c r="U14" s="935"/>
       <c r="V14" s="934">
-        <v>1234567</v>
+        <v>19120682489</v>
       </c>
       <c r="W14" s="1095"/>
       <c r="X14" s="1096"/>
@@ -45237,7 +45237,7 @@
       <c r="P27" s="1025"/>
       <c r="Q27" s="873"/>
       <c r="R27" s="1010">
-        <v>1234567</v>
+        <v>352005840</v>
       </c>
       <c r="S27" s="1010"/>
       <c r="T27" s="1010"/>
@@ -45995,7 +45995,7 @@
       <c r="B26" s="805"/>
       <c r="C26" s="806" t="str">
         <f>'Gen Inb'!O12&amp;"："&amp;'Gen Inb'!V12</f>
-        <v>示例船务代理有限公司：联系人</v>
+        <v>广州港中联国际船务代理有限公司：白树辉</v>
       </c>
       <c r="D26" s="807"/>
       <c r="E26" s="799"/>
@@ -46008,7 +46008,7 @@
       <c r="C27" s="799"/>
       <c r="D27" s="809">
         <f>'Gen Inb'!V14</f>
-        <v>1234567</v>
+        <v>19120682489</v>
       </c>
       <c r="E27" s="799"/>
       <c r="F27" s="798"/>
@@ -49805,7 +49805,7 @@
       <c r="H10" s="891"/>
       <c r="I10" s="892" t="str">
         <f>'Gen Inb'!I10</f>
-        <v>IMO:1234567</v>
+        <v>IMO:1116648</v>
       </c>
       <c r="J10" s="893"/>
       <c r="K10" s="893"/>
@@ -49965,7 +49965,7 @@
       <c r="O14" s="933"/>
       <c r="P14" s="934">
         <f>'Gen Inb'!P14</f>
-        <v>1234567</v>
+        <v>39080621</v>
       </c>
       <c r="Q14" s="935"/>
       <c r="R14" s="935"/>
@@ -49973,7 +49973,7 @@
       <c r="T14" s="935"/>
       <c r="U14" s="935"/>
       <c r="V14" s="936">
-        <v>1234567</v>
+        <v>18825058579</v>
       </c>
       <c r="W14" s="937"/>
       <c r="X14" s="938"/>
@@ -50100,7 +50100,7 @@
       <c r="S18" s="952"/>
       <c r="T18" s="955" t="str">
         <f>W8</f>
-        <v>示例国籍</v>
+        <v>中国香港</v>
       </c>
       <c r="U18" s="955"/>
       <c r="V18" s="955"/>
@@ -50436,7 +50436,7 @@
       <c r="P27" s="1018"/>
       <c r="Q27" s="873"/>
       <c r="R27" s="1010">
-        <v>1234567</v>
+        <v>305060000</v>
       </c>
       <c r="S27" s="1010"/>
       <c r="T27" s="1010"/>
@@ -51195,7 +51195,7 @@
       <c r="B26" s="805"/>
       <c r="C26" s="806" t="str">
         <f>'Gen Inb'!P12&amp;"："&amp;'Gen Inb'!V12</f>
-        <v>：联系人</v>
+        <v>：白树辉</v>
       </c>
       <c r="D26" s="807"/>
       <c r="E26" s="799"/>
@@ -51208,7 +51208,7 @@
       <c r="C27" s="799"/>
       <c r="D27" s="809">
         <f>'Gen Inb'!V14</f>
-        <v>1234567</v>
+        <v>19120682489</v>
       </c>
       <c r="E27" s="799"/>
       <c r="F27" s="798"/>
@@ -54746,7 +54746,7 @@
       <c r="C6" s="695"/>
       <c r="D6" s="696" t="str">
         <f>'Gen Inb'!I10</f>
-        <v>IMO:1234567</v>
+        <v>IMO:1116648</v>
       </c>
       <c r="E6" s="696"/>
       <c r="F6" s="697"/>

--- a/templates/tonnage_template.xlsx
+++ b/templates/tonnage_template.xlsx
@@ -400,7 +400,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>必须填写中国、中国香港、中国澳门三个值的其中一个</t>
+          <t>必须填写中国、示例国籍、中国澳门三个值的其中一个</t>
         </r>
         <r>
           <rPr>
@@ -1883,7 +1883,7 @@
     </r>
   </si>
   <si>
-    <t>IMO:1116648</t>
+    <t>IMO:1234567</t>
   </si>
   <si>
     <r>
@@ -2005,10 +2005,10 @@
     </r>
   </si>
   <si>
-    <t>广州港中联国际船务代理有限公司</t>
-  </si>
-  <si>
-    <t>白树辉</t>
+    <t>示例船务代理有限公司</t>
+  </si>
+  <si>
+    <t>联系人</t>
   </si>
   <si>
     <t>香港</t>
@@ -3237,7 +3237,7 @@
     </r>
   </si>
   <si>
-    <t>中国香港</t>
+    <t>示例国籍</t>
   </si>
   <si>
     <t>HONGKONG</t>
@@ -3487,7 +3487,7 @@
     <t>Montenegro</t>
   </si>
   <si>
-    <t>B42BR8005</t>
+    <t>TEST0001</t>
   </si>
   <si>
     <t>名单版本是正确的</t>
@@ -3505,7 +3505,7 @@
     <t>S</t>
   </si>
   <si>
-    <t>AB498691</t>
+    <t>TEST0002</t>
   </si>
   <si>
     <t>Second Officer</t>
@@ -3514,148 +3514,148 @@
     <t>Filipino</t>
   </si>
   <si>
-    <t>P0392496A</t>
-  </si>
-  <si>
-    <t>GONZAGA JOHN BRIAN CANALITA</t>
+    <t>TEST0003</t>
+  </si>
+  <si>
+    <t>赵六</t>
   </si>
   <si>
     <t>Third Officer</t>
   </si>
   <si>
-    <t>EC3697674</t>
-  </si>
-  <si>
-    <t>DYACHENKO VASYL</t>
+    <t>TEST0004</t>
+  </si>
+  <si>
+    <t>钱七</t>
   </si>
   <si>
     <t>Chief Engineer</t>
   </si>
   <si>
-    <t>AB406216</t>
-  </si>
-  <si>
-    <t>BALAKIN OLEG</t>
+    <t>TEST0005</t>
+  </si>
+  <si>
+    <t>孙八</t>
   </si>
   <si>
     <t>Second Engineer</t>
   </si>
   <si>
-    <t>AB565162</t>
-  </si>
-  <si>
-    <t>BACERDO OMAR DAMES</t>
+    <t>TEST0006</t>
+  </si>
+  <si>
+    <t>周九</t>
   </si>
   <si>
     <t>Junior Engineer</t>
   </si>
   <si>
-    <t>P1649209A</t>
-  </si>
-  <si>
-    <t>SANTACERA ROTSEN MAR DAYADAY</t>
+    <t>TEST0007</t>
+  </si>
+  <si>
+    <t>吴十</t>
   </si>
   <si>
     <t xml:space="preserve"> Junior Electrician</t>
   </si>
   <si>
-    <t>P1399821A</t>
-  </si>
-  <si>
-    <t>JAVIER EDGAR AMMEN</t>
+    <t>TEST0008</t>
+  </si>
+  <si>
+    <t>郑一</t>
   </si>
   <si>
     <t>Bosun</t>
   </si>
   <si>
-    <t>EC4641553</t>
-  </si>
-  <si>
-    <t>ELPA KENNETH BLANCO</t>
+    <t>TEST0009</t>
+  </si>
+  <si>
+    <t>王一</t>
   </si>
   <si>
     <t>Able Seaman</t>
   </si>
   <si>
-    <t>P2512380A</t>
-  </si>
-  <si>
-    <t>FLORENTINO JOEMARIE LACHICA</t>
-  </si>
-  <si>
-    <t>EC6525043</t>
-  </si>
-  <si>
-    <t>SUAREZ JETTE ANTHONY CAPANAS</t>
-  </si>
-  <si>
-    <t>P0863919A</t>
-  </si>
-  <si>
-    <t>JAMERO IANJAY HAMOAY</t>
+    <t>TEST0010</t>
+  </si>
+  <si>
+    <t>李一</t>
+  </si>
+  <si>
+    <t>TEST0011</t>
+  </si>
+  <si>
+    <t>赵一</t>
+  </si>
+  <si>
+    <t>TEST0012</t>
+  </si>
+  <si>
+    <t>陈一</t>
   </si>
   <si>
     <t>Ordinary Seaman</t>
   </si>
   <si>
-    <t>EC5956980</t>
-  </si>
-  <si>
-    <t>PELLETERO ALLEN SEGISMUNDO</t>
-  </si>
-  <si>
-    <t>P3925249A</t>
-  </si>
-  <si>
-    <t>OLOJAN ROSEN JUANICO</t>
+    <t>TEST0013</t>
+  </si>
+  <si>
+    <t>刘一</t>
+  </si>
+  <si>
+    <t>TEST0014</t>
+  </si>
+  <si>
+    <t>杨一</t>
   </si>
   <si>
     <t>Fitter</t>
   </si>
   <si>
-    <t>EC4389049</t>
-  </si>
-  <si>
-    <t>CAMILOTE GEOFFREY CALETINA</t>
+    <t>TEST0015</t>
+  </si>
+  <si>
+    <t>黄一</t>
   </si>
   <si>
     <t>Oiler</t>
   </si>
   <si>
-    <t>P2263420A</t>
-  </si>
-  <si>
-    <t>ECAT JOSEPH PAUL TENEBRO</t>
+    <t>TEST0016</t>
+  </si>
+  <si>
+    <t>周一</t>
   </si>
   <si>
     <t>Wiper</t>
   </si>
   <si>
-    <t>P3596511A</t>
-  </si>
-  <si>
-    <t>DELIS  EUGENE SALIGUMBA</t>
-  </si>
-  <si>
-    <t>EC5270716</t>
-  </si>
-  <si>
-    <t>MOGRO ROMELITO LOSTE</t>
+    <t>TEST0017</t>
+  </si>
+  <si>
+    <t>吴一</t>
+  </si>
+  <si>
+    <t>TEST0018</t>
+  </si>
+  <si>
+    <t>徐一</t>
   </si>
   <si>
     <t>Chief Cook</t>
   </si>
   <si>
-    <t>EC2844651</t>
-  </si>
-  <si>
-    <t>CAMANAY JONATHAN SUAZO</t>
+    <t>TEST0019</t>
+  </si>
+  <si>
+    <t>孙一</t>
   </si>
   <si>
     <t>Messboy</t>
   </si>
   <si>
-    <t>EC8290337</t>
+    <t>TEST0020</t>
   </si>
   <si>
     <t>12. Date and signature by master, authorized by agent or officer</t>
@@ -4074,7 +4074,7 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>/P4794223A</t>
+      <t>/TEST0001</t>
     </r>
   </si>
   <si>
@@ -4149,7 +4149,7 @@
     <t>Signature of Master:</t>
   </si>
   <si>
-    <t>Guangzhou Port Unitrans Agency Co., Ltd.</t>
+    <t>Example Shipping Agency Co., Ltd.</t>
   </si>
   <si>
     <r>
@@ -4190,25 +4190,25 @@
     <t>于洪涛</t>
   </si>
   <si>
-    <t>BILINS'KY ANDRIY</t>
-  </si>
-  <si>
-    <t>ET549562</t>
-  </si>
-  <si>
-    <t>OGANA ROGELIO PENTON</t>
+    <t>李四</t>
+  </si>
+  <si>
+    <t>TEST0008</t>
+  </si>
+  <si>
+    <t>王五</t>
   </si>
   <si>
     <t>DIACHENKO VASYL</t>
   </si>
   <si>
-    <t>ET112764</t>
-  </si>
-  <si>
-    <t>ET529509</t>
-  </si>
-  <si>
-    <t>BILANGO JEAN CONSULAR</t>
+    <t>TEST0009</t>
+  </si>
+  <si>
+    <t>TEST0010</t>
+  </si>
+  <si>
+    <t>王五</t>
   </si>
   <si>
     <t>F</t>
@@ -4223,10 +4223,10 @@
     <t>SAN MIGUEL BULACAN</t>
   </si>
   <si>
-    <t>EB9781010</t>
-  </si>
-  <si>
-    <t>交通运营单位：广州联合国际船舶代理有限公司</t>
+    <t>TEST0011</t>
+  </si>
+  <si>
+    <t>交通运营单位：示例船务代理有限公司</t>
   </si>
   <si>
     <t xml:space="preserve">移交时间：                        </t>
@@ -4567,7 +4567,7 @@
     <t>Container</t>
   </si>
   <si>
-    <t>IMO:9987574</t>
+    <t>IMO:1234567</t>
   </si>
   <si>
     <t>10086/782</t>
@@ -5074,7 +5074,7 @@
     <t>所有人</t>
   </si>
   <si>
-    <t>马士基中国航运</t>
+    <t>示例船公司中国航运</t>
   </si>
   <si>
     <t>Registration/IMO No.</t>
@@ -5448,7 +5448,7 @@
     <t>本表加附在报检面单之后</t>
   </si>
   <si>
-    <t>广州联合国际船舶代理有限公司</t>
+    <t>示例船务代理有限公司</t>
   </si>
   <si>
     <t>IN</t>
@@ -5469,7 +5469,7 @@
     <t>MANILA</t>
   </si>
   <si>
-    <t>金额：112092.8</t>
+    <t>金额：1000</t>
   </si>
   <si>
     <t>船舶吨税执照申请书</t>
@@ -5877,11 +5877,11 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>39080209</t>
+      <t>13800000000</t>
     </r>
   </si>
   <si>
-    <t>传真：（8620）39080620</t>
+    <t>传真：（8620）13800000000</t>
   </si>
   <si>
     <r>
@@ -5901,7 +5901,7 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>uniscogzns@vip.163.com</t>
+      <t>example@example.com</t>
     </r>
   </si>
   <si>
@@ -20244,7 +20244,7 @@
       </c>
       <c r="F8" s="1208" t="str">
         <f>'Gen Inb'!I10</f>
-        <v>IMO:1116648</v>
+        <v>IMO:1234567</v>
       </c>
       <c r="G8" s="1208"/>
       <c r="H8" s="1205"/>
@@ -21058,7 +21058,7 @@
     <row r="2" spans="1:11">
       <c r="A2" s="1217" t="str">
         <f>IF('Crew Inb'!K11="","",'Crew Inb'!K11)</f>
-        <v>B42BR8005</v>
+        <v>TEST0001</v>
       </c>
       <c r="B2" t="str">
         <f>IF('Crew Inb'!J11="","",IF('Crew Inb'!J11="P","普通护照",IF('Crew Inb'!J11="S","海员证","")))</f>
@@ -21090,7 +21090,7 @@
     <row r="3" spans="1:11">
       <c r="A3" t="str">
         <f>IF('Crew Inb'!K12="","",'Crew Inb'!K12)</f>
-        <v>AB498691</v>
+        <v>TEST0002</v>
       </c>
       <c r="B3" t="str">
         <f>IF('Crew Inb'!J12="","",IF('Crew Inb'!J12="P","普通护照",IF('Crew Inb'!J12="S","海员证","")))</f>
@@ -21122,7 +21122,7 @@
     <row r="4" spans="1:11">
       <c r="A4" t="str">
         <f>IF('Crew Inb'!K13="","",'Crew Inb'!K13)</f>
-        <v>P0392496A</v>
+        <v>TEST0003</v>
       </c>
       <c r="B4" t="str">
         <f>IF('Crew Inb'!J13="","",IF('Crew Inb'!J13="P","普通护照",IF('Crew Inb'!J13="S","海员证","")))</f>
@@ -21154,7 +21154,7 @@
     <row r="5" spans="1:11">
       <c r="A5" t="str">
         <f>IF('Crew Inb'!K14="","",'Crew Inb'!K14)</f>
-        <v>EC3697674</v>
+        <v>TEST0004</v>
       </c>
       <c r="B5" t="str">
         <f>IF('Crew Inb'!J14="","",IF('Crew Inb'!J14="P","普通护照",IF('Crew Inb'!J14="S","海员证","")))</f>
@@ -21165,7 +21165,7 @@
       </c>
       <c r="D5" t="str">
         <f>IF('Crew Inb'!C14="","",'Crew Inb'!C14&amp;" "&amp;'Crew Inb'!D14)</f>
-        <v>GONZAGA JOHN BRIAN CANALITA </v>
+        <v>赵六 </v>
       </c>
       <c r="E5" t="str">
         <f>IF('Crew Inb'!E14="","",IF('Crew Inb'!E14="M","男",IF('Crew Inb'!E14="F","女","未说明")))</f>
@@ -21186,7 +21186,7 @@
     <row r="6" spans="1:11">
       <c r="A6" t="str">
         <f>IF('Crew Inb'!K15="","",'Crew Inb'!K15)</f>
-        <v>AB406216</v>
+        <v>TEST0005</v>
       </c>
       <c r="B6" t="str">
         <f>IF('Crew Inb'!J15="","",IF('Crew Inb'!J15="P","普通护照",IF('Crew Inb'!J15="S","海员证","")))</f>
@@ -21197,7 +21197,7 @@
       </c>
       <c r="D6" t="str">
         <f>IF('Crew Inb'!C15="","",'Crew Inb'!C15&amp;" "&amp;'Crew Inb'!D15)</f>
-        <v>DYACHENKO VASYL </v>
+        <v>钱七 </v>
       </c>
       <c r="E6" t="str">
         <f>IF('Crew Inb'!E15="","",IF('Crew Inb'!E15="M","男",IF('Crew Inb'!E15="F","女","未说明")))</f>
@@ -21218,7 +21218,7 @@
     <row r="7" spans="1:11">
       <c r="A7" t="str">
         <f>IF('Crew Inb'!K16="","",'Crew Inb'!K16)</f>
-        <v>AB565162</v>
+        <v>TEST0006</v>
       </c>
       <c r="B7" t="str">
         <f>IF('Crew Inb'!J16="","",IF('Crew Inb'!J16="P","普通护照",IF('Crew Inb'!J16="S","海员证","")))</f>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="D7" t="str">
         <f>IF('Crew Inb'!C16="","",'Crew Inb'!C16&amp;" "&amp;'Crew Inb'!D16)</f>
-        <v>BALAKIN OLEG </v>
+        <v>孙八 </v>
       </c>
       <c r="E7" t="str">
         <f>IF('Crew Inb'!E16="","",IF('Crew Inb'!E16="M","男",IF('Crew Inb'!E16="F","女","未说明")))</f>
@@ -21250,7 +21250,7 @@
     <row r="8" spans="1:11">
       <c r="A8" t="str">
         <f>IF('Crew Inb'!K17="","",'Crew Inb'!K17)</f>
-        <v>P1649209A</v>
+        <v>TEST0007</v>
       </c>
       <c r="B8" t="str">
         <f>IF('Crew Inb'!J17="","",IF('Crew Inb'!J17="P","普通护照",IF('Crew Inb'!J17="S","海员证","")))</f>
@@ -21261,7 +21261,7 @@
       </c>
       <c r="D8" t="str">
         <f>IF('Crew Inb'!C17="","",'Crew Inb'!C17&amp;" "&amp;'Crew Inb'!D17)</f>
-        <v>BACERDO OMAR DAMES </v>
+        <v>周九 </v>
       </c>
       <c r="E8" t="str">
         <f>IF('Crew Inb'!E17="","",IF('Crew Inb'!E17="M","男",IF('Crew Inb'!E17="F","女","未说明")))</f>
@@ -21282,7 +21282,7 @@
     <row r="9" spans="1:11">
       <c r="A9" t="str">
         <f>IF('Crew Inb'!K18="","",'Crew Inb'!K18)</f>
-        <v>P1399821A</v>
+        <v>TEST0008</v>
       </c>
       <c r="B9" t="str">
         <f>IF('Crew Inb'!J18="","",IF('Crew Inb'!J18="P","普通护照",IF('Crew Inb'!J18="S","海员证","")))</f>
@@ -21293,7 +21293,7 @@
       </c>
       <c r="D9" t="str">
         <f>IF('Crew Inb'!C18="","",'Crew Inb'!C18&amp;" "&amp;'Crew Inb'!D18)</f>
-        <v>SANTACERA ROTSEN MAR DAYADAY </v>
+        <v>吴十 </v>
       </c>
       <c r="E9" t="str">
         <f>IF('Crew Inb'!E18="","",IF('Crew Inb'!E18="M","男",IF('Crew Inb'!E18="F","女","未说明")))</f>
@@ -21346,7 +21346,7 @@
     <row r="11" spans="1:11">
       <c r="A11" t="str">
         <f>IF('Crew Inb'!K19="","",'Crew Inb'!K19)</f>
-        <v>EC4641553</v>
+        <v>TEST0009</v>
       </c>
       <c r="B11" t="str">
         <f>IF('Crew Inb'!J19="","",IF('Crew Inb'!J19="P","普通护照",IF('Crew Inb'!J19="S","海员证","")))</f>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="D11" t="str">
         <f>IF('Crew Inb'!C19="","",'Crew Inb'!C19&amp;" "&amp;'Crew Inb'!D19)</f>
-        <v>JAVIER EDGAR AMMEN </v>
+        <v>郑一 </v>
       </c>
       <c r="E11" t="str">
         <f>IF('Crew Inb'!E19="","",IF('Crew Inb'!E19="M","男",IF('Crew Inb'!E19="F","女","未说明")))</f>
@@ -21378,7 +21378,7 @@
     <row r="12" spans="1:11">
       <c r="A12" t="str">
         <f>IF('Crew Inb'!K20="","",'Crew Inb'!K20)</f>
-        <v>P2512380A</v>
+        <v>TEST0010</v>
       </c>
       <c r="B12" t="str">
         <f>IF('Crew Inb'!J20="","",IF('Crew Inb'!J20="P","普通护照",IF('Crew Inb'!J20="S","海员证","")))</f>
@@ -21389,7 +21389,7 @@
       </c>
       <c r="D12" t="str">
         <f>IF('Crew Inb'!C20="","",'Crew Inb'!C20&amp;" "&amp;'Crew Inb'!D20)</f>
-        <v>ELPA KENNETH BLANCO </v>
+        <v>王一 </v>
       </c>
       <c r="E12" t="str">
         <f>IF('Crew Inb'!E20="","",IF('Crew Inb'!E20="M","男",IF('Crew Inb'!E20="F","女","未说明")))</f>
@@ -21410,7 +21410,7 @@
     <row r="13" spans="1:11">
       <c r="A13" t="str">
         <f>IF('Crew Inb'!K21="","",'Crew Inb'!K21)</f>
-        <v>EC6525043</v>
+        <v>TEST0011</v>
       </c>
       <c r="B13" t="str">
         <f>IF('Crew Inb'!J21="","",IF('Crew Inb'!J21="P","普通护照",IF('Crew Inb'!J21="S","海员证","")))</f>
@@ -21421,7 +21421,7 @@
       </c>
       <c r="D13" t="str">
         <f>IF('Crew Inb'!C21="","",'Crew Inb'!C21&amp;" "&amp;'Crew Inb'!D21)</f>
-        <v>FLORENTINO JOEMARIE LACHICA </v>
+        <v>李一 </v>
       </c>
       <c r="E13" t="str">
         <f>IF('Crew Inb'!E21="","",IF('Crew Inb'!E21="M","男",IF('Crew Inb'!E21="F","女","未说明")))</f>
@@ -21442,7 +21442,7 @@
     <row r="14" spans="1:11">
       <c r="A14" t="str">
         <f>IF('Crew Inb'!K22="","",'Crew Inb'!K22)</f>
-        <v>P0863919A</v>
+        <v>TEST0012</v>
       </c>
       <c r="B14" t="str">
         <f>IF('Crew Inb'!J22="","",IF('Crew Inb'!J22="P","普通护照",IF('Crew Inb'!J22="S","海员证","")))</f>
@@ -21453,7 +21453,7 @@
       </c>
       <c r="D14" t="str">
         <f>IF('Crew Inb'!C22="","",'Crew Inb'!C22&amp;" "&amp;'Crew Inb'!D22)</f>
-        <v>SUAREZ JETTE ANTHONY CAPANAS </v>
+        <v>赵一 </v>
       </c>
       <c r="E14" t="str">
         <f>IF('Crew Inb'!E22="","",IF('Crew Inb'!E22="M","男",IF('Crew Inb'!E22="F","女","未说明")))</f>
@@ -21474,7 +21474,7 @@
     <row r="15" spans="1:11">
       <c r="A15" t="str">
         <f>IF('Crew Inb'!K23="","",'Crew Inb'!K23)</f>
-        <v>EC5956980</v>
+        <v>TEST0013</v>
       </c>
       <c r="B15" t="str">
         <f>IF('Crew Inb'!J23="","",IF('Crew Inb'!J23="P","普通护照",IF('Crew Inb'!J23="S","海员证","")))</f>
@@ -21485,7 +21485,7 @@
       </c>
       <c r="D15" t="str">
         <f>IF('Crew Inb'!C23="","",'Crew Inb'!C23&amp;" "&amp;'Crew Inb'!D23)</f>
-        <v>JAMERO IANJAY HAMOAY </v>
+        <v>陈一 </v>
       </c>
       <c r="E15" t="str">
         <f>IF('Crew Inb'!E23="","",IF('Crew Inb'!E23="M","男",IF('Crew Inb'!E23="F","女","未说明")))</f>
@@ -21506,7 +21506,7 @@
     <row r="16" spans="1:11">
       <c r="A16" t="str">
         <f>IF('Crew Inb'!K24="","",'Crew Inb'!K24)</f>
-        <v>P3925249A</v>
+        <v>TEST0014</v>
       </c>
       <c r="B16" t="str">
         <f>IF('Crew Inb'!J24="","",IF('Crew Inb'!J24="P","普通护照",IF('Crew Inb'!J24="S","海员证","")))</f>
@@ -21517,7 +21517,7 @@
       </c>
       <c r="D16" t="str">
         <f>IF('Crew Inb'!C24="","",'Crew Inb'!C24&amp;" "&amp;'Crew Inb'!D24)</f>
-        <v>PELLETERO ALLEN SEGISMUNDO </v>
+        <v>刘一 </v>
       </c>
       <c r="E16" t="str">
         <f>IF('Crew Inb'!E24="","",IF('Crew Inb'!E24="M","男",IF('Crew Inb'!E24="F","女","未说明")))</f>
@@ -21538,7 +21538,7 @@
     <row r="17" spans="1:8">
       <c r="A17" t="str">
         <f>IF('Crew Inb'!K25="","",'Crew Inb'!K25)</f>
-        <v>EC4389049</v>
+        <v>TEST0015</v>
       </c>
       <c r="B17" t="str">
         <f>IF('Crew Inb'!J25="","",IF('Crew Inb'!J25="P","普通护照",IF('Crew Inb'!J25="S","海员证","")))</f>
@@ -21549,7 +21549,7 @@
       </c>
       <c r="D17" t="str">
         <f>IF('Crew Inb'!C25="","",'Crew Inb'!C25&amp;" "&amp;'Crew Inb'!D25)</f>
-        <v>OLOJAN ROSEN JUANICO </v>
+        <v>杨一 </v>
       </c>
       <c r="E17" t="str">
         <f>IF('Crew Inb'!E25="","",IF('Crew Inb'!E25="M","男",IF('Crew Inb'!E25="F","女","未说明")))</f>
@@ -21570,7 +21570,7 @@
     <row r="18" spans="1:8">
       <c r="A18" t="str">
         <f>IF('Crew Inb'!K26="","",'Crew Inb'!K26)</f>
-        <v>P2263420A</v>
+        <v>TEST0016</v>
       </c>
       <c r="B18" t="str">
         <f>IF('Crew Inb'!J26="","",IF('Crew Inb'!J26="P","普通护照",IF('Crew Inb'!J26="S","海员证","")))</f>
@@ -21581,7 +21581,7 @@
       </c>
       <c r="D18" t="str">
         <f>IF('Crew Inb'!C26="","",'Crew Inb'!C26&amp;" "&amp;'Crew Inb'!D26)</f>
-        <v>CAMILOTE GEOFFREY CALETINA </v>
+        <v>黄一 </v>
       </c>
       <c r="E18" t="str">
         <f>IF('Crew Inb'!E26="","",IF('Crew Inb'!E26="M","男",IF('Crew Inb'!E26="F","女","未说明")))</f>
@@ -21602,7 +21602,7 @@
     <row r="19" spans="1:8">
       <c r="A19" t="str">
         <f>IF('Crew Inb'!K27="","",'Crew Inb'!K27)</f>
-        <v>P3596511A</v>
+        <v>TEST0017</v>
       </c>
       <c r="B19" t="str">
         <f>IF('Crew Inb'!J27="","",IF('Crew Inb'!J27="P","普通护照",IF('Crew Inb'!J27="S","海员证","")))</f>
@@ -21613,7 +21613,7 @@
       </c>
       <c r="D19" t="str">
         <f>IF('Crew Inb'!C27="","",'Crew Inb'!C27&amp;" "&amp;'Crew Inb'!D27)</f>
-        <v>ECAT JOSEPH PAUL TENEBRO </v>
+        <v>周一 </v>
       </c>
       <c r="E19" t="str">
         <f>IF('Crew Inb'!E27="","",IF('Crew Inb'!E27="M","男",IF('Crew Inb'!E27="F","女","未说明")))</f>
@@ -22845,7 +22845,7 @@
       <c r="C6" s="569"/>
       <c r="D6" s="570" t="str">
         <f>'Gen Inb'!I10</f>
-        <v>IMO:1116648</v>
+        <v>IMO:1234567</v>
       </c>
       <c r="E6" s="570"/>
       <c r="F6" s="571"/>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="R9" s="418" t="str">
         <f>'Gen Inb'!I10</f>
-        <v>IMO:1116648</v>
+        <v>IMO:1234567</v>
       </c>
       <c r="S9" s="418"/>
       <c r="T9" s="418"/>
@@ -29245,7 +29245,7 @@
       <c r="F21" s="393"/>
       <c r="G21" s="401"/>
       <c r="H21" s="393">
-        <v>1050189</v>
+        <v>1234567</v>
       </c>
       <c r="I21" s="393"/>
       <c r="J21" s="396">
@@ -29256,7 +29256,7 @@
     <row r="22" ht="24" customHeight="1" spans="2:13">
       <c r="B22" s="401"/>
       <c r="C22" s="393">
-        <v>1047976</v>
+        <v>1234567</v>
       </c>
       <c r="D22" s="393"/>
       <c r="E22" s="396">
@@ -29265,7 +29265,7 @@
       <c r="F22" s="393"/>
       <c r="G22" s="401"/>
       <c r="H22" s="393">
-        <v>1048985</v>
+        <v>1234567</v>
       </c>
       <c r="I22" s="393"/>
       <c r="J22" s="396">
@@ -29275,7 +29275,7 @@
     <row r="23" ht="24" customHeight="1" spans="2:13">
       <c r="B23" s="401"/>
       <c r="C23" s="393">
-        <v>1049874</v>
+        <v>1234567</v>
       </c>
       <c r="D23" s="393"/>
       <c r="E23" s="397">
@@ -29284,7 +29284,7 @@
       <c r="F23" s="393"/>
       <c r="G23" s="401"/>
       <c r="H23" s="393">
-        <v>1049867</v>
+        <v>1234567</v>
       </c>
       <c r="I23" s="393"/>
       <c r="J23" s="397">
@@ -29294,7 +29294,7 @@
     <row r="24" ht="24" customHeight="1" spans="2:13">
       <c r="B24" s="401"/>
       <c r="C24" s="393">
-        <v>1049872</v>
+        <v>1234567</v>
       </c>
       <c r="D24" s="393"/>
       <c r="E24" s="397">
@@ -29318,7 +29318,7 @@
       <c r="F25" s="393"/>
       <c r="G25" s="401"/>
       <c r="H25" s="393">
-        <v>1049874</v>
+        <v>1234567</v>
       </c>
       <c r="I25" s="393"/>
       <c r="J25" s="397">
@@ -32580,7 +32580,7 @@
       <c r="D6" s="286"/>
       <c r="E6" s="294" t="str">
         <f>'Gen Outb'!M18&amp;"/"&amp;'Gen Outb'!T18</f>
-        <v>南沙新港/中国香港</v>
+        <v>南沙新港/示例国籍</v>
       </c>
       <c r="F6" s="295"/>
       <c r="G6" s="295"/>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="D17" s="260" t="str">
         <f>'Gen Inb'!I10</f>
-        <v>IMO:1116648</v>
+        <v>IMO:1234567</v>
       </c>
       <c r="E17" s="255" t="s">
         <v>615</v>
@@ -35477,7 +35477,7 @@
         <v>635</v>
       </c>
       <c r="G26" s="259" t="str">
-        <f>IF(G25="广州联合国际船舶代理有限公司","UNISCOGZ","")</f>
+        <f>IF(G25="示例船务代理有限公司","UNISCOGZ","")</f>
         <v/>
       </c>
     </row>
@@ -35487,14 +35487,14 @@
       </c>
       <c r="D27" s="263" t="str">
         <f>'Gen Inb'!V12</f>
-        <v>白树辉</v>
+        <v>联系人</v>
       </c>
       <c r="E27" s="255" t="s">
         <v>637</v>
       </c>
       <c r="F27" s="268">
         <f>'Gen Inb'!V14</f>
-        <v>19120682489</v>
+        <v>1234567</v>
       </c>
       <c r="G27" s="268"/>
     </row>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="D17" s="260" t="str">
         <f>'Gen Inb'!I10</f>
-        <v>IMO:1116648</v>
+        <v>IMO:1234567</v>
       </c>
       <c r="E17" s="255" t="s">
         <v>615</v>
@@ -35764,7 +35764,7 @@
       </c>
       <c r="D21" s="256" t="str">
         <f>'Gen Outb'!W8</f>
-        <v>中国香港</v>
+        <v>示例国籍</v>
       </c>
       <c r="E21" s="255" t="s">
         <v>658</v>
@@ -35838,7 +35838,7 @@
         <v>635</v>
       </c>
       <c r="G26" s="259" t="str">
-        <f>IF(G25="广州联合国际船舶代理有限公司","UNISCOGZ","")</f>
+        <f>IF(G25="示例船务代理有限公司","UNISCOGZ","")</f>
         <v/>
       </c>
     </row>
@@ -35848,14 +35848,14 @@
       </c>
       <c r="D27" s="263" t="str">
         <f>'Gen Inb'!V12</f>
-        <v>白树辉</v>
+        <v>联系人</v>
       </c>
       <c r="E27" s="255" t="s">
         <v>637</v>
       </c>
       <c r="F27" s="268">
         <f>'Gen Inb'!V14</f>
-        <v>19120682489</v>
+        <v>1234567</v>
       </c>
       <c r="G27" s="268"/>
     </row>
@@ -36371,7 +36371,7 @@
       <c r="F4" s="162"/>
       <c r="J4" s="178" t="str">
         <f>'Parts A'!B5</f>
-        <v>IMO:9987574</v>
+        <v>IMO:1234567</v>
       </c>
       <c r="K4" s="178"/>
       <c r="L4" s="178"/>
@@ -36435,7 +36435,7 @@
       <c r="F9" s="178"/>
       <c r="G9" s="164" t="str">
         <f>'Gen Inb'!P12&amp;"："&amp;'Gen Inb'!V12</f>
-        <v>：白树辉</v>
+        <v>：联系人</v>
       </c>
       <c r="H9" s="164"/>
       <c r="I9" s="164"/>
@@ -36456,7 +36456,7 @@
       <c r="F10" s="176"/>
       <c r="G10" s="178" t="str">
         <f>'Gen Inb'!P14&amp;"  "&amp;'Gen Inb'!V14</f>
-        <v>39080621  19120682489</v>
+        <v>13800000000  13800000000</v>
       </c>
       <c r="H10" s="178"/>
       <c r="I10" s="178"/>
@@ -36668,7 +36668,7 @@
       <c r="F4" s="162"/>
       <c r="J4" s="178" t="str">
         <f>'IMO Gen Inb'!J4</f>
-        <v>IMO:9987574</v>
+        <v>IMO:1234567</v>
       </c>
       <c r="K4" s="178"/>
       <c r="L4" s="178"/>
@@ -36718,7 +36718,7 @@
       <c r="F7" s="164"/>
       <c r="J7" s="162" t="str">
         <f>'Gen Outb'!W8&amp;""&amp;'Gen Outb'!W9</f>
-        <v>中国香港HONGKONG</v>
+        <v>示例国籍HONGKONG</v>
       </c>
       <c r="K7" s="162"/>
       <c r="L7" s="162"/>
@@ -36732,7 +36732,7 @@
       <c r="F9" s="178"/>
       <c r="G9" s="164" t="str">
         <f>'Gen Inb'!P12&amp;"："&amp;'Gen Inb'!V12</f>
-        <v>：白树辉</v>
+        <v>：联系人</v>
       </c>
       <c r="H9" s="164"/>
       <c r="I9" s="164"/>
@@ -36753,7 +36753,7 @@
       <c r="F10" s="176"/>
       <c r="G10" s="178" t="str">
         <f>'Gen Inb'!P14&amp;"  "&amp;'Gen Inb'!V14</f>
-        <v>39080621  19120682489</v>
+        <v>13800000000  13800000000</v>
       </c>
       <c r="H10" s="178"/>
       <c r="I10" s="178"/>
@@ -36779,7 +36779,7 @@
     <row r="13" ht="47.25" customHeight="1" spans="2:12">
       <c r="B13" s="164" t="str">
         <f>'Gen Outb'!M18&amp;"  "&amp;"("&amp;'Gen Outb'!M19&amp;")"&amp;"——"&amp;'Gen Outb'!T18&amp;"  "&amp;"("&amp;'Gen Outb'!T19&amp;")"</f>
-        <v>南沙新港  (NANSHA NEW PORT)——中国香港  (HONGKONG)</v>
+        <v>南沙新港  (NANSHA NEW PORT)——示例国籍  (HONGKONG)</v>
       </c>
       <c r="C13" s="164"/>
       <c r="D13" s="164"/>
@@ -36954,7 +36954,7 @@
       <c r="D3" s="179"/>
       <c r="G3" s="177" t="str">
         <f>'IMO Gen Inb'!J4</f>
-        <v>IMO:9987574</v>
+        <v>IMO:1234567</v>
       </c>
       <c r="J3" s="177" t="str">
         <f>'IMO Gen Inb'!C5</f>
@@ -37020,13 +37020,13 @@
     <row r="23" customHeight="1" spans="4:10">
       <c r="D23" s="177" t="str">
         <f>'Gen Inb'!P12&amp;"："&amp;'Gen Inb'!V12</f>
-        <v>：白树辉</v>
+        <v>：联系人</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="4:10">
       <c r="D24" s="177" t="str">
         <f>'Gen Inb'!P14&amp;"，"&amp;'Gen Inb'!V14</f>
-        <v>39080621，19120682489</v>
+        <v>13800000000，13800000000</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="4:10">
@@ -37088,7 +37088,7 @@
       <c r="D3" s="179"/>
       <c r="G3" s="178" t="str">
         <f>'IMO Gen Outb'!J4</f>
-        <v>IMO:9987574</v>
+        <v>IMO:1234567</v>
       </c>
       <c r="J3" s="177" t="str">
         <f>'IMO Gen Outb'!C5</f>
@@ -37116,7 +37116,7 @@
       </c>
       <c r="H5" s="162" t="str">
         <f>'IMO Gen Outb'!J7</f>
-        <v>中国香港HONGKONG</v>
+        <v>示例国籍HONGKONG</v>
       </c>
       <c r="I5" s="162"/>
       <c r="J5" s="162"/>
@@ -37154,13 +37154,13 @@
     <row r="23" customHeight="1" spans="4:13">
       <c r="D23" s="177" t="str">
         <f>'Gen Inb'!P12&amp;"："&amp;'Gen Inb'!V12</f>
-        <v>：白树辉</v>
+        <v>：联系人</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="4:13">
       <c r="D24" s="177" t="str">
         <f>'Gen Inb'!P14&amp;"，"&amp;'Gen Inb'!V14</f>
-        <v>39080621，19120682489</v>
+        <v>13800000000，13800000000</v>
       </c>
       <c r="M24" s="177" t="s">
         <v>684</v>
@@ -37234,7 +37234,7 @@
       <c r="G4" s="163"/>
       <c r="H4" s="164" t="str">
         <f>'IMO Gen Inb'!J4</f>
-        <v>IMO:9987574</v>
+        <v>IMO:1234567</v>
       </c>
       <c r="L4" s="164" t="str">
         <f>'IMO Gen Inb'!C5</f>
@@ -37313,7 +37313,7 @@
       </c>
       <c r="K8" s="1219" t="str">
         <f>IF('Crew Inb'!K11&lt;&gt;"",'Crew Inb'!K11,"")</f>
-        <v>B42BR8005</v>
+        <v>TEST0001</v>
       </c>
       <c r="L8" s="166"/>
     </row>
@@ -37352,7 +37352,7 @@
       </c>
       <c r="K9" s="166" t="str">
         <f>IF('Crew Inb'!K12&lt;&gt;"",'Crew Inb'!K12,"")</f>
-        <v>AB498691</v>
+        <v>TEST0002</v>
       </c>
       <c r="L9" s="166"/>
     </row>
@@ -37391,7 +37391,7 @@
       </c>
       <c r="K10" s="166" t="str">
         <f>IF('Crew Inb'!K13&lt;&gt;"",'Crew Inb'!K13,"")</f>
-        <v>P0392496A</v>
+        <v>TEST0003</v>
       </c>
       <c r="L10" s="166"/>
     </row>
@@ -37402,7 +37402,7 @@
       </c>
       <c r="C11" s="167" t="str">
         <f>IF('Crew Inb'!C14&lt;&gt;"",'Crew Inb'!C14&amp;" "&amp;'Crew Inb'!D14,"")</f>
-        <v>GONZAGA JOHN BRIAN CANALITA </v>
+        <v>赵六 </v>
       </c>
       <c r="D11" s="166" t="str">
         <f>IF('Crew Inb'!E14&lt;&gt;"",'Crew Inb'!E14,"")</f>
@@ -37430,7 +37430,7 @@
       </c>
       <c r="K11" s="166" t="str">
         <f>IF('Crew Inb'!K14&lt;&gt;"",'Crew Inb'!K14,"")</f>
-        <v>EC3697674</v>
+        <v>TEST0004</v>
       </c>
       <c r="L11" s="166"/>
     </row>
@@ -37441,7 +37441,7 @@
       </c>
       <c r="C12" s="167" t="str">
         <f>IF('Crew Inb'!C15&lt;&gt;"",'Crew Inb'!C15&amp;" "&amp;'Crew Inb'!D15,"")</f>
-        <v>DYACHENKO VASYL </v>
+        <v>钱七 </v>
       </c>
       <c r="D12" s="166" t="str">
         <f>IF('Crew Inb'!E15&lt;&gt;"",'Crew Inb'!E15,"")</f>
@@ -37469,7 +37469,7 @@
       </c>
       <c r="K12" s="166" t="str">
         <f>IF('Crew Inb'!K15&lt;&gt;"",'Crew Inb'!K15,"")</f>
-        <v>AB406216</v>
+        <v>TEST0005</v>
       </c>
       <c r="L12" s="166"/>
     </row>
@@ -37480,7 +37480,7 @@
       </c>
       <c r="C13" s="167" t="str">
         <f>IF('Crew Inb'!C16&lt;&gt;"",'Crew Inb'!C16&amp;" "&amp;'Crew Inb'!D16,"")</f>
-        <v>BALAKIN OLEG </v>
+        <v>孙八 </v>
       </c>
       <c r="D13" s="166" t="str">
         <f>IF('Crew Inb'!E16&lt;&gt;"",'Crew Inb'!E16,"")</f>
@@ -37508,7 +37508,7 @@
       </c>
       <c r="K13" s="166" t="str">
         <f>IF('Crew Inb'!K16&lt;&gt;"",'Crew Inb'!K16,"")</f>
-        <v>AB565162</v>
+        <v>TEST0006</v>
       </c>
       <c r="L13" s="166"/>
     </row>
@@ -37519,7 +37519,7 @@
       </c>
       <c r="C14" s="167" t="str">
         <f>IF('Crew Inb'!C17&lt;&gt;"",'Crew Inb'!C17&amp;" "&amp;'Crew Inb'!D17,"")</f>
-        <v>BACERDO OMAR DAMES </v>
+        <v>周九 </v>
       </c>
       <c r="D14" s="166" t="str">
         <f>IF('Crew Inb'!E17&lt;&gt;"",'Crew Inb'!E17,"")</f>
@@ -37547,7 +37547,7 @@
       </c>
       <c r="K14" s="166" t="str">
         <f>IF('Crew Inb'!K17&lt;&gt;"",'Crew Inb'!K17,"")</f>
-        <v>P1649209A</v>
+        <v>TEST0007</v>
       </c>
       <c r="L14" s="166"/>
     </row>
@@ -37558,7 +37558,7 @@
       </c>
       <c r="C15" s="167" t="str">
         <f>IF('Crew Inb'!C18&lt;&gt;"",'Crew Inb'!C18&amp;" "&amp;'Crew Inb'!D18,"")</f>
-        <v>SANTACERA ROTSEN MAR DAYADAY </v>
+        <v>吴十 </v>
       </c>
       <c r="D15" s="166" t="str">
         <f>IF('Crew Inb'!E18&lt;&gt;"",'Crew Inb'!E18,"")</f>
@@ -37586,7 +37586,7 @@
       </c>
       <c r="K15" s="166" t="str">
         <f>IF('Crew Inb'!K18&lt;&gt;"",'Crew Inb'!K18,"")</f>
-        <v>P1399821A</v>
+        <v>TEST0008</v>
       </c>
       <c r="L15" s="166"/>
     </row>
@@ -37597,7 +37597,7 @@
       </c>
       <c r="C16" s="167" t="str">
         <f>IF('Crew Inb'!C19&lt;&gt;"",'Crew Inb'!C19&amp;" "&amp;'Crew Inb'!D19,"")</f>
-        <v>JAVIER EDGAR AMMEN </v>
+        <v>郑一 </v>
       </c>
       <c r="D16" s="166" t="str">
         <f>IF('Crew Inb'!E19&lt;&gt;"",'Crew Inb'!E19,"")</f>
@@ -37625,7 +37625,7 @@
       </c>
       <c r="K16" s="166" t="str">
         <f>IF('Crew Inb'!K19&lt;&gt;"",'Crew Inb'!K19,"")</f>
-        <v>EC4641553</v>
+        <v>TEST0009</v>
       </c>
       <c r="L16" s="166"/>
     </row>
@@ -37636,7 +37636,7 @@
       </c>
       <c r="C17" s="167" t="str">
         <f>IF('Crew Inb'!C20&lt;&gt;"",'Crew Inb'!C20&amp;" "&amp;'Crew Inb'!D20,"")</f>
-        <v>ELPA KENNETH BLANCO </v>
+        <v>王一 </v>
       </c>
       <c r="D17" s="166" t="str">
         <f>IF('Crew Inb'!E20&lt;&gt;"",'Crew Inb'!E20,"")</f>
@@ -37664,7 +37664,7 @@
       </c>
       <c r="K17" s="166" t="str">
         <f>IF('Crew Inb'!K20&lt;&gt;"",'Crew Inb'!K20,"")</f>
-        <v>P2512380A</v>
+        <v>TEST0010</v>
       </c>
       <c r="L17" s="166"/>
     </row>
@@ -37675,7 +37675,7 @@
       </c>
       <c r="C18" s="167" t="str">
         <f>IF('Crew Inb'!C21&lt;&gt;"",'Crew Inb'!C21&amp;" "&amp;'Crew Inb'!D21,"")</f>
-        <v>FLORENTINO JOEMARIE LACHICA </v>
+        <v>李一 </v>
       </c>
       <c r="D18" s="166" t="str">
         <f>IF('Crew Inb'!E21&lt;&gt;"",'Crew Inb'!E21,"")</f>
@@ -37703,7 +37703,7 @@
       </c>
       <c r="K18" s="166" t="str">
         <f>IF('Crew Inb'!K21&lt;&gt;"",'Crew Inb'!K21,"")</f>
-        <v>EC6525043</v>
+        <v>TEST0011</v>
       </c>
       <c r="L18" s="166"/>
     </row>
@@ -37714,7 +37714,7 @@
       </c>
       <c r="C19" s="167" t="str">
         <f>IF('Crew Inb'!C22&lt;&gt;"",'Crew Inb'!C22&amp;" "&amp;'Crew Inb'!D22,"")</f>
-        <v>SUAREZ JETTE ANTHONY CAPANAS </v>
+        <v>赵一 </v>
       </c>
       <c r="D19" s="166" t="str">
         <f>IF('Crew Inb'!E22&lt;&gt;"",'Crew Inb'!E22,"")</f>
@@ -37742,7 +37742,7 @@
       </c>
       <c r="K19" s="166" t="str">
         <f>IF('Crew Inb'!K22&lt;&gt;"",'Crew Inb'!K22,"")</f>
-        <v>P0863919A</v>
+        <v>TEST0012</v>
       </c>
       <c r="L19" s="166"/>
     </row>
@@ -37753,7 +37753,7 @@
       </c>
       <c r="C20" s="167" t="str">
         <f>IF('Crew Inb'!C23&lt;&gt;"",'Crew Inb'!C23&amp;" "&amp;'Crew Inb'!D23,"")</f>
-        <v>JAMERO IANJAY HAMOAY </v>
+        <v>陈一 </v>
       </c>
       <c r="D20" s="166" t="str">
         <f>IF('Crew Inb'!E23&lt;&gt;"",'Crew Inb'!E23,"")</f>
@@ -37781,7 +37781,7 @@
       </c>
       <c r="K20" s="166" t="str">
         <f>IF('Crew Inb'!K23&lt;&gt;"",'Crew Inb'!K23,"")</f>
-        <v>EC5956980</v>
+        <v>TEST0013</v>
       </c>
       <c r="L20" s="166"/>
     </row>
@@ -37792,7 +37792,7 @@
       </c>
       <c r="C21" s="167" t="str">
         <f>IF('Crew Inb'!C24&lt;&gt;"",'Crew Inb'!C24&amp;" "&amp;'Crew Inb'!D24,"")</f>
-        <v>PELLETERO ALLEN SEGISMUNDO </v>
+        <v>刘一 </v>
       </c>
       <c r="D21" s="166" t="str">
         <f>IF('Crew Inb'!E24&lt;&gt;"",'Crew Inb'!E24,"")</f>
@@ -37820,7 +37820,7 @@
       </c>
       <c r="K21" s="166" t="str">
         <f>IF('Crew Inb'!K24&lt;&gt;"",'Crew Inb'!K24,"")</f>
-        <v>P3925249A</v>
+        <v>TEST0014</v>
       </c>
       <c r="L21" s="166"/>
     </row>
@@ -37831,7 +37831,7 @@
       </c>
       <c r="C22" s="167" t="str">
         <f>IF('Crew Inb'!C25&lt;&gt;"",'Crew Inb'!C25&amp;" "&amp;'Crew Inb'!D25,"")</f>
-        <v>OLOJAN ROSEN JUANICO </v>
+        <v>杨一 </v>
       </c>
       <c r="D22" s="166" t="str">
         <f>IF('Crew Inb'!E25&lt;&gt;"",'Crew Inb'!E25,"")</f>
@@ -37859,7 +37859,7 @@
       </c>
       <c r="K22" s="166" t="str">
         <f>IF('Crew Inb'!K25&lt;&gt;"",'Crew Inb'!K25,"")</f>
-        <v>EC4389049</v>
+        <v>TEST0015</v>
       </c>
       <c r="L22" s="166"/>
     </row>
@@ -37870,7 +37870,7 @@
       </c>
       <c r="C23" s="167" t="str">
         <f>IF('Crew Inb'!C26&lt;&gt;"",'Crew Inb'!C26&amp;" "&amp;'Crew Inb'!D26,"")</f>
-        <v>CAMILOTE GEOFFREY CALETINA </v>
+        <v>黄一 </v>
       </c>
       <c r="D23" s="166" t="str">
         <f>IF('Crew Inb'!E26&lt;&gt;"",'Crew Inb'!E26,"")</f>
@@ -37898,7 +37898,7 @@
       </c>
       <c r="K23" s="166" t="str">
         <f>IF('Crew Inb'!K26&lt;&gt;"",'Crew Inb'!K26,"")</f>
-        <v>P2263420A</v>
+        <v>TEST0016</v>
       </c>
       <c r="L23" s="166"/>
     </row>
@@ -37909,7 +37909,7 @@
       </c>
       <c r="C24" s="167" t="str">
         <f>IF('Crew Inb'!C27&lt;&gt;"",'Crew Inb'!C27&amp;" "&amp;'Crew Inb'!D27,"")</f>
-        <v>ECAT JOSEPH PAUL TENEBRO </v>
+        <v>周一 </v>
       </c>
       <c r="D24" s="166" t="str">
         <f>IF('Crew Inb'!E27&lt;&gt;"",'Crew Inb'!E27,"")</f>
@@ -37937,7 +37937,7 @@
       </c>
       <c r="K24" s="166" t="str">
         <f>IF('Crew Inb'!K27&lt;&gt;"",'Crew Inb'!K27,"")</f>
-        <v>P3596511A</v>
+        <v>TEST0017</v>
       </c>
       <c r="L24" s="166"/>
     </row>
@@ -37948,7 +37948,7 @@
       </c>
       <c r="C25" s="167" t="str">
         <f>IF('Crew Inb'!C28&lt;&gt;"",'Crew Inb'!C28&amp;" "&amp;'Crew Inb'!D28,"")</f>
-        <v>DELIS  EUGENE SALIGUMBA </v>
+        <v>吴一 </v>
       </c>
       <c r="D25" s="166" t="str">
         <f>IF('Crew Inb'!E28&lt;&gt;"",'Crew Inb'!E28,"")</f>
@@ -37976,7 +37976,7 @@
       </c>
       <c r="K25" s="166" t="str">
         <f>IF('Crew Inb'!K28&lt;&gt;"",'Crew Inb'!K28,"")</f>
-        <v>EC5270716</v>
+        <v>TEST0018</v>
       </c>
       <c r="L25" s="166"/>
     </row>
@@ -37987,7 +37987,7 @@
       </c>
       <c r="C26" s="167" t="str">
         <f>IF('Crew Inb'!C29&lt;&gt;"",'Crew Inb'!C29&amp;" "&amp;'Crew Inb'!D29,"")</f>
-        <v>MOGRO ROMELITO LOSTE </v>
+        <v>徐一 </v>
       </c>
       <c r="D26" s="166" t="str">
         <f>IF('Crew Inb'!E29&lt;&gt;"",'Crew Inb'!E29,"")</f>
@@ -38015,7 +38015,7 @@
       </c>
       <c r="K26" s="166" t="str">
         <f>IF('Crew Inb'!K29&lt;&gt;"",'Crew Inb'!K29,"")</f>
-        <v>EC2844651</v>
+        <v>TEST0019</v>
       </c>
       <c r="L26" s="166"/>
     </row>
@@ -38085,7 +38085,7 @@
       <c r="G31" s="163"/>
       <c r="H31" s="164" t="str">
         <f>'IMO Gen Inb'!J4</f>
-        <v>IMO:9987574</v>
+        <v>IMO:1234567</v>
       </c>
       <c r="I31" s="163"/>
       <c r="J31" s="163"/>
@@ -38140,7 +38140,7 @@
       </c>
       <c r="C35" s="167" t="str">
         <f>IF('Crew Inb'!C30&lt;&gt;"",'Crew Inb'!C30&amp;" "&amp;'Crew Inb'!D30,"")</f>
-        <v>CAMANAY JONATHAN SUAZO </v>
+        <v>孙一 </v>
       </c>
       <c r="D35" s="166" t="s">
         <v>232</v>
@@ -38167,7 +38167,7 @@
       </c>
       <c r="K35" s="166" t="str">
         <f>IF('Crew Inb'!K30&lt;&gt;"",'Crew Inb'!K30,"")</f>
-        <v>EC8290337</v>
+        <v>TEST0020</v>
       </c>
       <c r="L35" s="166"/>
     </row>
@@ -38526,7 +38526,7 @@
       <c r="G4" s="163"/>
       <c r="H4" s="164" t="str">
         <f>'IMO Gen Outb'!J4</f>
-        <v>IMO:9987574</v>
+        <v>IMO:1234567</v>
       </c>
       <c r="L4" s="164" t="str">
         <f>'IMO Gen Outb'!C5</f>
@@ -38563,7 +38563,7 @@
       <c r="G6" s="163"/>
       <c r="I6" s="162" t="str">
         <f>'IMO Gen Outb'!J7</f>
-        <v>中国香港HONGKONG</v>
+        <v>示例国籍HONGKONG</v>
       </c>
       <c r="J6" s="162"/>
       <c r="K6" s="162"/>
@@ -38605,7 +38605,7 @@
       </c>
       <c r="K8" s="1219" t="str">
         <f>IF('Crew Inb'!K11&lt;&gt;"",'Crew Inb'!K11,"")</f>
-        <v>B42BR8005</v>
+        <v>TEST0001</v>
       </c>
       <c r="L8" s="166"/>
     </row>
@@ -38644,7 +38644,7 @@
       </c>
       <c r="K9" s="166" t="str">
         <f>IF('Crew Inb'!K12&lt;&gt;"",'Crew Inb'!K12,"")</f>
-        <v>AB498691</v>
+        <v>TEST0002</v>
       </c>
       <c r="L9" s="166"/>
     </row>
@@ -38683,7 +38683,7 @@
       </c>
       <c r="K10" s="166" t="str">
         <f>IF('Crew Inb'!K13&lt;&gt;"",'Crew Inb'!K13,"")</f>
-        <v>P0392496A</v>
+        <v>TEST0003</v>
       </c>
       <c r="L10" s="166"/>
     </row>
@@ -38694,7 +38694,7 @@
       </c>
       <c r="C11" s="167" t="str">
         <f>IF('Crew Inb'!C14&lt;&gt;"",'Crew Inb'!C14&amp;" "&amp;'Crew Inb'!D14,"")</f>
-        <v>GONZAGA JOHN BRIAN CANALITA </v>
+        <v>赵六 </v>
       </c>
       <c r="D11" s="166" t="str">
         <f>IF('Crew Inb'!E14&lt;&gt;"",'Crew Inb'!E14,"")</f>
@@ -38722,7 +38722,7 @@
       </c>
       <c r="K11" s="166" t="str">
         <f>IF('Crew Inb'!K14&lt;&gt;"",'Crew Inb'!K14,"")</f>
-        <v>EC3697674</v>
+        <v>TEST0004</v>
       </c>
       <c r="L11" s="166"/>
     </row>
@@ -38733,7 +38733,7 @@
       </c>
       <c r="C12" s="167" t="str">
         <f>IF('Crew Inb'!C15&lt;&gt;"",'Crew Inb'!C15&amp;" "&amp;'Crew Inb'!D15,"")</f>
-        <v>DYACHENKO VASYL </v>
+        <v>钱七 </v>
       </c>
       <c r="D12" s="166" t="str">
         <f>IF('Crew Inb'!E15&lt;&gt;"",'Crew Inb'!E15,"")</f>
@@ -38761,7 +38761,7 @@
       </c>
       <c r="K12" s="166" t="str">
         <f>IF('Crew Inb'!K15&lt;&gt;"",'Crew Inb'!K15,"")</f>
-        <v>AB406216</v>
+        <v>TEST0005</v>
       </c>
       <c r="L12" s="166"/>
     </row>
@@ -38772,7 +38772,7 @@
       </c>
       <c r="C13" s="167" t="str">
         <f>IF('Crew Inb'!C16&lt;&gt;"",'Crew Inb'!C16&amp;" "&amp;'Crew Inb'!D16,"")</f>
-        <v>BALAKIN OLEG </v>
+        <v>孙八 </v>
       </c>
       <c r="D13" s="166" t="str">
         <f>IF('Crew Inb'!E16&lt;&gt;"",'Crew Inb'!E16,"")</f>
@@ -38800,7 +38800,7 @@
       </c>
       <c r="K13" s="166" t="str">
         <f>IF('Crew Inb'!K16&lt;&gt;"",'Crew Inb'!K16,"")</f>
-        <v>AB565162</v>
+        <v>TEST0006</v>
       </c>
       <c r="L13" s="166"/>
     </row>
@@ -38811,7 +38811,7 @@
       </c>
       <c r="C14" s="167" t="str">
         <f>IF('Crew Inb'!C17&lt;&gt;"",'Crew Inb'!C17&amp;" "&amp;'Crew Inb'!D17,"")</f>
-        <v>BACERDO OMAR DAMES </v>
+        <v>周九 </v>
       </c>
       <c r="D14" s="166" t="str">
         <f>IF('Crew Inb'!E17&lt;&gt;"",'Crew Inb'!E17,"")</f>
@@ -38839,7 +38839,7 @@
       </c>
       <c r="K14" s="166" t="str">
         <f>IF('Crew Inb'!K17&lt;&gt;"",'Crew Inb'!K17,"")</f>
-        <v>P1649209A</v>
+        <v>TEST0007</v>
       </c>
       <c r="L14" s="166"/>
     </row>
@@ -38850,7 +38850,7 @@
       </c>
       <c r="C15" s="167" t="str">
         <f>IF('Crew Inb'!C18&lt;&gt;"",'Crew Inb'!C18&amp;" "&amp;'Crew Inb'!D18,"")</f>
-        <v>SANTACERA ROTSEN MAR DAYADAY </v>
+        <v>吴十 </v>
       </c>
       <c r="D15" s="166" t="str">
         <f>IF('Crew Inb'!E18&lt;&gt;"",'Crew Inb'!E18,"")</f>
@@ -38878,7 +38878,7 @@
       </c>
       <c r="K15" s="166" t="str">
         <f>IF('Crew Inb'!K18&lt;&gt;"",'Crew Inb'!K18,"")</f>
-        <v>P1399821A</v>
+        <v>TEST0008</v>
       </c>
       <c r="L15" s="166"/>
     </row>
@@ -38889,7 +38889,7 @@
       </c>
       <c r="C16" s="167" t="str">
         <f>IF('Crew Inb'!C19&lt;&gt;"",'Crew Inb'!C19&amp;" "&amp;'Crew Inb'!D19,"")</f>
-        <v>JAVIER EDGAR AMMEN </v>
+        <v>郑一 </v>
       </c>
       <c r="D16" s="166" t="str">
         <f>IF('Crew Inb'!E19&lt;&gt;"",'Crew Inb'!E19,"")</f>
@@ -38917,7 +38917,7 @@
       </c>
       <c r="K16" s="166" t="str">
         <f>IF('Crew Inb'!K19&lt;&gt;"",'Crew Inb'!K19,"")</f>
-        <v>EC4641553</v>
+        <v>TEST0009</v>
       </c>
       <c r="L16" s="166"/>
     </row>
@@ -38928,7 +38928,7 @@
       </c>
       <c r="C17" s="167" t="str">
         <f>IF('Crew Inb'!C20&lt;&gt;"",'Crew Inb'!C20&amp;" "&amp;'Crew Inb'!D20,"")</f>
-        <v>ELPA KENNETH BLANCO </v>
+        <v>王一 </v>
       </c>
       <c r="D17" s="166" t="str">
         <f>IF('Crew Inb'!E20&lt;&gt;"",'Crew Inb'!E20,"")</f>
@@ -38956,7 +38956,7 @@
       </c>
       <c r="K17" s="166" t="str">
         <f>IF('Crew Inb'!K20&lt;&gt;"",'Crew Inb'!K20,"")</f>
-        <v>P2512380A</v>
+        <v>TEST0010</v>
       </c>
       <c r="L17" s="166"/>
     </row>
@@ -38967,7 +38967,7 @@
       </c>
       <c r="C18" s="167" t="str">
         <f>IF('Crew Inb'!C21&lt;&gt;"",'Crew Inb'!C21&amp;" "&amp;'Crew Inb'!D21,"")</f>
-        <v>FLORENTINO JOEMARIE LACHICA </v>
+        <v>李一 </v>
       </c>
       <c r="D18" s="166" t="str">
         <f>IF('Crew Inb'!E21&lt;&gt;"",'Crew Inb'!E21,"")</f>
@@ -38995,7 +38995,7 @@
       </c>
       <c r="K18" s="166" t="str">
         <f>IF('Crew Inb'!K21&lt;&gt;"",'Crew Inb'!K21,"")</f>
-        <v>EC6525043</v>
+        <v>TEST0011</v>
       </c>
       <c r="L18" s="166"/>
     </row>
@@ -39006,7 +39006,7 @@
       </c>
       <c r="C19" s="167" t="str">
         <f>IF('Crew Inb'!C22&lt;&gt;"",'Crew Inb'!C22&amp;" "&amp;'Crew Inb'!D22,"")</f>
-        <v>SUAREZ JETTE ANTHONY CAPANAS </v>
+        <v>赵一 </v>
       </c>
       <c r="D19" s="166" t="str">
         <f>IF('Crew Inb'!E22&lt;&gt;"",'Crew Inb'!E22,"")</f>
@@ -39034,7 +39034,7 @@
       </c>
       <c r="K19" s="166" t="str">
         <f>IF('Crew Inb'!K22&lt;&gt;"",'Crew Inb'!K22,"")</f>
-        <v>P0863919A</v>
+        <v>TEST0012</v>
       </c>
       <c r="L19" s="166"/>
     </row>
@@ -39045,7 +39045,7 @@
       </c>
       <c r="C20" s="167" t="str">
         <f>IF('Crew Inb'!C23&lt;&gt;"",'Crew Inb'!C23&amp;" "&amp;'Crew Inb'!D23,"")</f>
-        <v>JAMERO IANJAY HAMOAY </v>
+        <v>陈一 </v>
       </c>
       <c r="D20" s="166" t="str">
         <f>IF('Crew Inb'!E23&lt;&gt;"",'Crew Inb'!E23,"")</f>
@@ -39073,7 +39073,7 @@
       </c>
       <c r="K20" s="166" t="str">
         <f>IF('Crew Inb'!K23&lt;&gt;"",'Crew Inb'!K23,"")</f>
-        <v>EC5956980</v>
+        <v>TEST0013</v>
       </c>
       <c r="L20" s="166"/>
     </row>
@@ -39084,7 +39084,7 @@
       </c>
       <c r="C21" s="167" t="str">
         <f>IF('Crew Inb'!C24&lt;&gt;"",'Crew Inb'!C24&amp;" "&amp;'Crew Inb'!D24,"")</f>
-        <v>PELLETERO ALLEN SEGISMUNDO </v>
+        <v>刘一 </v>
       </c>
       <c r="D21" s="166" t="str">
         <f>IF('Crew Inb'!E24&lt;&gt;"",'Crew Inb'!E24,"")</f>
@@ -39112,7 +39112,7 @@
       </c>
       <c r="K21" s="166" t="str">
         <f>IF('Crew Inb'!K24&lt;&gt;"",'Crew Inb'!K24,"")</f>
-        <v>P3925249A</v>
+        <v>TEST0014</v>
       </c>
       <c r="L21" s="166"/>
     </row>
@@ -39123,7 +39123,7 @@
       </c>
       <c r="C22" s="167" t="str">
         <f>IF('Crew Inb'!C25&lt;&gt;"",'Crew Inb'!C25&amp;" "&amp;'Crew Inb'!D25,"")</f>
-        <v>OLOJAN ROSEN JUANICO </v>
+        <v>杨一 </v>
       </c>
       <c r="D22" s="166" t="str">
         <f>IF('Crew Inb'!E25&lt;&gt;"",'Crew Inb'!E25,"")</f>
@@ -39151,7 +39151,7 @@
       </c>
       <c r="K22" s="166" t="str">
         <f>IF('Crew Inb'!K25&lt;&gt;"",'Crew Inb'!K25,"")</f>
-        <v>EC4389049</v>
+        <v>TEST0015</v>
       </c>
       <c r="L22" s="166"/>
     </row>
@@ -39162,7 +39162,7 @@
       </c>
       <c r="C23" s="167" t="str">
         <f>IF('Crew Inb'!C26&lt;&gt;"",'Crew Inb'!C26&amp;" "&amp;'Crew Inb'!D26,"")</f>
-        <v>CAMILOTE GEOFFREY CALETINA </v>
+        <v>黄一 </v>
       </c>
       <c r="D23" s="166" t="str">
         <f>IF('Crew Inb'!E26&lt;&gt;"",'Crew Inb'!E26,"")</f>
@@ -39190,7 +39190,7 @@
       </c>
       <c r="K23" s="166" t="str">
         <f>IF('Crew Inb'!K26&lt;&gt;"",'Crew Inb'!K26,"")</f>
-        <v>P2263420A</v>
+        <v>TEST0016</v>
       </c>
       <c r="L23" s="166"/>
     </row>
@@ -39201,7 +39201,7 @@
       </c>
       <c r="C24" s="167" t="str">
         <f>IF('Crew Inb'!C27&lt;&gt;"",'Crew Inb'!C27&amp;" "&amp;'Crew Inb'!D27,"")</f>
-        <v>ECAT JOSEPH PAUL TENEBRO </v>
+        <v>周一 </v>
       </c>
       <c r="D24" s="166" t="str">
         <f>IF('Crew Inb'!E27&lt;&gt;"",'Crew Inb'!E27,"")</f>
@@ -39229,7 +39229,7 @@
       </c>
       <c r="K24" s="166" t="str">
         <f>IF('Crew Inb'!K27&lt;&gt;"",'Crew Inb'!K27,"")</f>
-        <v>P3596511A</v>
+        <v>TEST0017</v>
       </c>
       <c r="L24" s="166"/>
     </row>
@@ -39240,7 +39240,7 @@
       </c>
       <c r="C25" s="167" t="str">
         <f>IF('Crew Inb'!C28&lt;&gt;"",'Crew Inb'!C28&amp;" "&amp;'Crew Inb'!D28,"")</f>
-        <v>DELIS  EUGENE SALIGUMBA </v>
+        <v>吴一 </v>
       </c>
       <c r="D25" s="166" t="str">
         <f>IF('Crew Inb'!E28&lt;&gt;"",'Crew Inb'!E28,"")</f>
@@ -39268,7 +39268,7 @@
       </c>
       <c r="K25" s="166" t="str">
         <f>IF('Crew Inb'!K28&lt;&gt;"",'Crew Inb'!K28,"")</f>
-        <v>EC5270716</v>
+        <v>TEST0018</v>
       </c>
       <c r="L25" s="166"/>
     </row>
@@ -39279,7 +39279,7 @@
       </c>
       <c r="C26" s="167" t="str">
         <f>IF('Crew Inb'!C29&lt;&gt;"",'Crew Inb'!C29&amp;" "&amp;'Crew Inb'!D29,"")</f>
-        <v>MOGRO ROMELITO LOSTE </v>
+        <v>徐一 </v>
       </c>
       <c r="D26" s="166" t="str">
         <f>IF('Crew Inb'!E29&lt;&gt;"",'Crew Inb'!E29,"")</f>
@@ -39307,7 +39307,7 @@
       </c>
       <c r="K26" s="166" t="str">
         <f>IF('Crew Inb'!K29&lt;&gt;"",'Crew Inb'!K29,"")</f>
-        <v>EC2844651</v>
+        <v>TEST0019</v>
       </c>
       <c r="L26" s="166"/>
     </row>
@@ -39348,7 +39348,7 @@
       <c r="G31" s="163"/>
       <c r="H31" s="164" t="str">
         <f>'IMO Gen Outb'!J4</f>
-        <v>IMO:9987574</v>
+        <v>IMO:1234567</v>
       </c>
       <c r="I31" s="163"/>
       <c r="J31" s="163"/>
@@ -39390,7 +39390,7 @@
       <c r="H33" s="163"/>
       <c r="I33" s="162" t="str">
         <f>'IMO Gen Outb'!J7</f>
-        <v>中国香港HONGKONG</v>
+        <v>示例国籍HONGKONG</v>
       </c>
       <c r="J33" s="162"/>
       <c r="K33" s="162"/>
@@ -39403,7 +39403,7 @@
       </c>
       <c r="C35" s="167" t="str">
         <f>IF('Crew Inb'!C30&lt;&gt;"",'Crew Inb'!C30&amp;" "&amp;'Crew Inb'!D30,"")</f>
-        <v>CAMANAY JONATHAN SUAZO </v>
+        <v>孙一 </v>
       </c>
       <c r="D35" s="166" t="s">
         <v>232</v>
@@ -39427,7 +39427,7 @@
       </c>
       <c r="K35" s="166" t="str">
         <f>IF('Crew Inb'!K30&lt;&gt;"",'Crew Inb'!K30,"")</f>
-        <v>EC8290337</v>
+        <v>TEST0020</v>
       </c>
       <c r="L35" s="166"/>
     </row>
@@ -39814,7 +39814,7 @@
       </c>
       <c r="H5" s="1134" t="str">
         <f>'Gen Outb'!W8</f>
-        <v>中国香港</v>
+        <v>示例国籍</v>
       </c>
       <c r="I5" s="1137"/>
       <c r="J5" s="1131"/>
@@ -40470,7 +40470,7 @@
       </c>
       <c r="B4" s="103"/>
       <c r="C4" s="104">
-        <v>9790074</v>
+        <v>1234567</v>
       </c>
       <c r="D4" s="104"/>
       <c r="E4" s="104"/>
@@ -41464,7 +41464,7 @@
       </c>
       <c r="H15" s="86" t="str">
         <f>'Gen Outb'!W8</f>
-        <v>中国香港</v>
+        <v>示例国籍</v>
       </c>
       <c r="I15" s="86"/>
       <c r="J15" s="86"/>
@@ -41550,7 +41550,7 @@
       </c>
       <c r="D30" s="68">
         <f>'Gen Inb'!R27</f>
-        <v>352005840</v>
+        <v>1234567</v>
       </c>
     </row>
     <row r="32" spans="3:8">
@@ -41603,7 +41603,7 @@
       <c r="H46" s="62"/>
       <c r="M46" s="76" t="str">
         <f>'Gen Inb'!V12&amp;"  "&amp;'Gen Inb'!V14</f>
-        <v>白树辉  19120682489</v>
+        <v>联系人  13800000000</v>
       </c>
     </row>
     <row r="48" spans="3:13">
@@ -41817,7 +41817,7 @@
       <c r="G18" s="65"/>
       <c r="H18" s="80" t="str">
         <f>'Gen Outb'!W8</f>
-        <v>中国香港</v>
+        <v>示例国籍</v>
       </c>
       <c r="I18" s="80"/>
       <c r="J18" s="80"/>
@@ -41848,7 +41848,7 @@
       <c r="H28" s="62"/>
       <c r="M28" s="76" t="str">
         <f>'Gen Inb'!V12&amp;"  "&amp;'Gen Inb'!V14</f>
-        <v>白树辉  19120682489</v>
+        <v>联系人  13800000000</v>
       </c>
     </row>
     <row r="30" spans="3:13">
@@ -42024,7 +42024,7 @@
       </c>
       <c r="H15" s="64" t="str">
         <f>'Gen Outb'!W8</f>
-        <v>中国香港</v>
+        <v>示例国籍</v>
       </c>
       <c r="I15" s="64"/>
       <c r="J15" s="64"/>
@@ -42158,7 +42158,7 @@
       <c r="H46" s="62"/>
       <c r="M46" s="76" t="str">
         <f>'Gen Inb'!V12&amp;"  "&amp;'Gen Inb'!V14</f>
-        <v>白树辉  19120682489</v>
+        <v>联系人  13800000000</v>
       </c>
     </row>
     <row r="48" spans="4:13">
@@ -43479,7 +43479,7 @@
       </c>
       <c r="E3" s="7" t="str">
         <f>'Parts A'!B5</f>
-        <v>IMO:9987574</v>
+        <v>IMO:1234567</v>
       </c>
       <c r="F3" s="8"/>
     </row>
@@ -44774,7 +44774,7 @@
       <c r="N14" s="932"/>
       <c r="O14" s="933"/>
       <c r="P14" s="934">
-        <v>39080621</v>
+        <v>1234567</v>
       </c>
       <c r="Q14" s="935"/>
       <c r="R14" s="935"/>
@@ -44782,7 +44782,7 @@
       <c r="T14" s="935"/>
       <c r="U14" s="935"/>
       <c r="V14" s="934">
-        <v>19120682489</v>
+        <v>1234567</v>
       </c>
       <c r="W14" s="1095"/>
       <c r="X14" s="1096"/>
@@ -45237,7 +45237,7 @@
       <c r="P27" s="1025"/>
       <c r="Q27" s="873"/>
       <c r="R27" s="1010">
-        <v>352005840</v>
+        <v>1234567</v>
       </c>
       <c r="S27" s="1010"/>
       <c r="T27" s="1010"/>
@@ -45995,7 +45995,7 @@
       <c r="B26" s="805"/>
       <c r="C26" s="806" t="str">
         <f>'Gen Inb'!O12&amp;"："&amp;'Gen Inb'!V12</f>
-        <v>广州港中联国际船务代理有限公司：白树辉</v>
+        <v>示例船务代理有限公司：联系人</v>
       </c>
       <c r="D26" s="807"/>
       <c r="E26" s="799"/>
@@ -46008,7 +46008,7 @@
       <c r="C27" s="799"/>
       <c r="D27" s="809">
         <f>'Gen Inb'!V14</f>
-        <v>19120682489</v>
+        <v>1234567</v>
       </c>
       <c r="E27" s="799"/>
       <c r="F27" s="798"/>
@@ -49805,7 +49805,7 @@
       <c r="H10" s="891"/>
       <c r="I10" s="892" t="str">
         <f>'Gen Inb'!I10</f>
-        <v>IMO:1116648</v>
+        <v>IMO:1234567</v>
       </c>
       <c r="J10" s="893"/>
       <c r="K10" s="893"/>
@@ -49965,7 +49965,7 @@
       <c r="O14" s="933"/>
       <c r="P14" s="934">
         <f>'Gen Inb'!P14</f>
-        <v>39080621</v>
+        <v>1234567</v>
       </c>
       <c r="Q14" s="935"/>
       <c r="R14" s="935"/>
@@ -49973,7 +49973,7 @@
       <c r="T14" s="935"/>
       <c r="U14" s="935"/>
       <c r="V14" s="936">
-        <v>18825058579</v>
+        <v>1234567</v>
       </c>
       <c r="W14" s="937"/>
       <c r="X14" s="938"/>
@@ -50100,7 +50100,7 @@
       <c r="S18" s="952"/>
       <c r="T18" s="955" t="str">
         <f>W8</f>
-        <v>中国香港</v>
+        <v>示例国籍</v>
       </c>
       <c r="U18" s="955"/>
       <c r="V18" s="955"/>
@@ -50436,7 +50436,7 @@
       <c r="P27" s="1018"/>
       <c r="Q27" s="873"/>
       <c r="R27" s="1010">
-        <v>305060000</v>
+        <v>1234567</v>
       </c>
       <c r="S27" s="1010"/>
       <c r="T27" s="1010"/>
@@ -51195,7 +51195,7 @@
       <c r="B26" s="805"/>
       <c r="C26" s="806" t="str">
         <f>'Gen Inb'!P12&amp;"："&amp;'Gen Inb'!V12</f>
-        <v>：白树辉</v>
+        <v>：联系人</v>
       </c>
       <c r="D26" s="807"/>
       <c r="E26" s="799"/>
@@ -51208,7 +51208,7 @@
       <c r="C27" s="799"/>
       <c r="D27" s="809">
         <f>'Gen Inb'!V14</f>
-        <v>19120682489</v>
+        <v>1234567</v>
       </c>
       <c r="E27" s="799"/>
       <c r="F27" s="798"/>
@@ -54746,7 +54746,7 @@
       <c r="C6" s="695"/>
       <c r="D6" s="696" t="str">
         <f>'Gen Inb'!I10</f>
-        <v>IMO:1116648</v>
+        <v>IMO:1234567</v>
       </c>
       <c r="E6" s="696"/>
       <c r="F6" s="697"/>
